--- a/output/2026-10-01/enriched_analysis.xlsx
+++ b/output/2026-10-01/enriched_analysis.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR52"/>
+  <dimension ref="A1:BR51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -889,25 +889,25 @@
         <v>88.13</v>
       </c>
       <c r="J2" t="n">
-        <v>75.77</v>
+        <v>76.3</v>
       </c>
       <c r="K2" t="n">
-        <v>16.3</v>
+        <v>15.5</v>
       </c>
       <c r="L2" t="n">
         <v>61.32</v>
       </c>
       <c r="M2" t="n">
-        <v>88.06</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>880556810</v>
+        <v>779924810</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>880556810</v>
+        <v>779924810</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>3.005</v>
+        <v>2.664</v>
       </c>
       <c r="W2" t="n">
-        <v>2930</v>
+        <v>2928</v>
       </c>
       <c r="X2" t="n">
         <v>22.9</v>
@@ -971,10 +971,10 @@
         <v>128.3</v>
       </c>
       <c r="AJ2" t="n">
-        <v>75.76913270892582</v>
+        <v>76.30180841958143</v>
       </c>
       <c r="AK2" t="n">
-        <v>16.3</v>
+        <v>15.5</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="AR2" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="AS2" t="n">
         <v>22</v>
@@ -1396,7 +1396,7 @@
         <v>0.049</v>
       </c>
       <c r="W4" t="n">
-        <v>2730</v>
+        <v>2729</v>
       </c>
       <c r="X4" t="n">
         <v>9.380000000000001</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.95</v>
+        <v>0.952</v>
       </c>
       <c r="W5" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="X5" t="n">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Y5" t="n">
         <v>22</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="W6" t="n">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="X6" t="n">
-        <v>9.51</v>
+        <v>9.52</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.979</v>
+        <v>0.993</v>
       </c>
       <c r="W7" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="X7" t="n">
-        <v>8.720000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>2.232</v>
+        <v>2.212</v>
       </c>
       <c r="W8" t="n">
-        <v>2630</v>
+        <v>2653</v>
       </c>
       <c r="X8" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Y8" t="n">
         <v>6</v>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.471</v>
+        <v>0.472</v>
       </c>
       <c r="W9" t="n">
-        <v>2757</v>
+        <v>2753</v>
       </c>
       <c r="X9" t="n">
         <v>22.6</v>
@@ -2788,10 +2788,10 @@
         <v>0.067</v>
       </c>
       <c r="W10" t="n">
-        <v>850</v>
+        <v>843</v>
       </c>
       <c r="X10" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="Y10" t="n">
         <v>19</v>
@@ -3018,10 +3018,10 @@
         <v>0.046</v>
       </c>
       <c r="W11" t="n">
-        <v>15781</v>
+        <v>15734</v>
       </c>
       <c r="X11" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="Y11" t="n">
         <v>83</v>
@@ -3480,10 +3480,10 @@
         <v>0.125</v>
       </c>
       <c r="W13" t="n">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="X13" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Y13" t="n">
         <v>17</v>
@@ -3706,7 +3706,7 @@
         <v>0.046</v>
       </c>
       <c r="W14" t="n">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="X14" t="n">
         <v>23.9</v>
@@ -3938,7 +3938,7 @@
         <v>0.12</v>
       </c>
       <c r="W15" t="n">
-        <v>2623</v>
+        <v>2621</v>
       </c>
       <c r="X15" t="n">
         <v>23</v>
@@ -4167,13 +4167,13 @@
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2.84</v>
+        <v>2.835</v>
       </c>
       <c r="W16" t="n">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="X16" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Y16" t="n">
         <v>30</v>
@@ -4393,13 +4393,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.493</v>
+        <v>0.495</v>
       </c>
       <c r="W17" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="X17" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="Y17" t="n">
         <v>21</v>
@@ -4628,10 +4628,10 @@
         <v>0.062</v>
       </c>
       <c r="W18" t="n">
-        <v>1776</v>
+        <v>1782</v>
       </c>
       <c r="X18" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="Y18" t="n">
         <v>20</v>
@@ -5089,13 +5089,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.377</v>
+        <v>0.374</v>
       </c>
       <c r="W20" t="n">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="X20" t="n">
-        <v>53.2</v>
+        <v>53.6</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.65</v>
+        <v>0.649</v>
       </c>
       <c r="W21" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="X21" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="Y21" t="n">
         <v>19</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="X22" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="Y22" t="n">
         <v>-5</v>
@@ -5788,7 +5788,7 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>53129</v>
+        <v>53106</v>
       </c>
       <c r="X23" t="n">
         <v>45</v>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.914</v>
+        <v>0.927</v>
       </c>
       <c r="W25" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="X25" t="n">
-        <v>6.36</v>
+        <v>6.27</v>
       </c>
       <c r="Y25" t="n">
         <v>31</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.647</v>
+        <v>0.643</v>
       </c>
       <c r="W26" t="n">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="X26" t="n">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="Y26" t="n">
         <v>-61</v>
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>1.893</v>
+        <v>1.876</v>
       </c>
       <c r="W27" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
@@ -6863,16 +6863,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -6880,169 +6880,171 @@
         </is>
       </c>
       <c r="E28" t="n">
+        <v>9</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="J28" t="n">
+        <v>96.03</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L28" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>26023230</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>26023230</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>19</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>704.35</v>
-      </c>
-      <c r="J28" t="n">
-        <v>782.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L28" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5375657</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>5375657</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S28" t="b">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="W28" t="n">
+        <v>950</v>
+      </c>
+      <c r="X28" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-36</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>96.02667896678967</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AL28" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="AP28" t="inlineStr">
+        <is>
+          <t>29-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS28" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="W28" t="n">
-        <v>713</v>
-      </c>
-      <c r="X28" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>185</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>204</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AE28" t="b">
+      <c r="AT28" t="n">
         <v>1</v>
       </c>
-      <c r="AF28" t="n">
-        <v>16.07</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>724.12</v>
-      </c>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="n">
-        <v>-22.5</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>782.5967389721939</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>-10</v>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>29-06-2026</t>
-        </is>
-      </c>
-      <c r="AP28" t="inlineStr">
-        <is>
-          <t>17-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>94</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
       <c r="AU28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>6202680</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1751854</v>
+        <v>26023230</v>
       </c>
       <c r="BA28" t="n">
-        <v>1751854</v>
+        <v>26023230</v>
       </c>
       <c r="BB28" t="n">
-        <v>1751854</v>
+        <v>26023230</v>
       </c>
       <c r="BC28" t="n">
-        <v>1751854</v>
+        <v>26023230</v>
       </c>
       <c r="BD28" t="n">
         <v>0</v>
@@ -7075,10 +7077,10 @@
         <v>0</v>
       </c>
       <c r="BN28" t="n">
-        <v>0</v>
+        <v>6202680</v>
       </c>
       <c r="BO28" t="n">
-        <v>1751854</v>
+        <v>26023230</v>
       </c>
       <c r="BP28" t="n">
         <v>1</v>
@@ -7087,22 +7089,22 @@
         <v>0</v>
       </c>
       <c r="BR28" t="n">
-        <v>0</v>
+        <v>0.2384</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7113,7 +7115,7 @@
         <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>5</v>
@@ -7122,28 +7124,28 @@
         <v>-1</v>
       </c>
       <c r="I29" t="n">
-        <v>26.25</v>
+        <v>171.1</v>
       </c>
       <c r="J29" t="n">
-        <v>29.64</v>
+        <v>174.27</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.4</v>
+        <v>-1.8</v>
       </c>
       <c r="L29" t="n">
-        <v>61.81</v>
+        <v>61.48</v>
       </c>
       <c r="M29" t="n">
-        <v>0.74</v>
+        <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>7410250</v>
+        <v>10743104</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>7410250</v>
+        <v>10743104</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -7157,60 +7159,60 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.266</v>
+        <v>0.495</v>
       </c>
       <c r="W29" t="n">
-        <v>279</v>
+        <v>217</v>
       </c>
       <c r="X29" t="n">
-        <v>14.7</v>
+        <v>37.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>16</v>
+        <v>-44</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.79</v>
+        <v>-3.28</v>
       </c>
       <c r="AA29" t="n">
-        <v>-30</v>
+        <v>141</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.21</v>
+        <v>-4.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>18</v>
+        <v>8.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="AE29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.83</v>
+        <v>-35.96</v>
       </c>
       <c r="AG29" t="n">
-        <v>27.98</v>
+        <v>173.05</v>
       </c>
       <c r="AH29" t="n">
-        <v>31.94</v>
+        <v>178.42</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.8</v>
+        <v>30.1</v>
       </c>
       <c r="AJ29" t="n">
-        <v>29.641</v>
+        <v>174.2652478588113</v>
       </c>
       <c r="AK29" t="n">
-        <v>-11.4</v>
+        <v>-1.8</v>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
@@ -7219,62 +7221,62 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>92</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="AS29" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AT29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY29" t="n">
-        <v>1331000</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2651250</v>
+        <v>9361398</v>
       </c>
       <c r="BA29" t="n">
-        <v>3342250</v>
+        <v>10743104</v>
       </c>
       <c r="BB29" t="n">
-        <v>5545000</v>
+        <v>10743104</v>
       </c>
       <c r="BC29" t="n">
-        <v>5545000</v>
+        <v>10743104</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
@@ -7307,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="BN29" t="n">
-        <v>1331000</v>
+        <v>0</v>
       </c>
       <c r="BO29" t="n">
-        <v>3342250</v>
+        <v>10743104</v>
       </c>
       <c r="BP29" t="n">
         <v>1</v>
@@ -7319,22 +7321,22 @@
         <v>0</v>
       </c>
       <c r="BR29" t="n">
-        <v>0.3982</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7342,40 +7344,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
         <v>-1</v>
       </c>
       <c r="I30" t="n">
-        <v>93.16</v>
+        <v>26.25</v>
       </c>
       <c r="J30" t="n">
-        <v>96.13</v>
+        <v>27.72</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.1</v>
+        <v>-5.3</v>
       </c>
       <c r="L30" t="n">
-        <v>71.89</v>
+        <v>61.81</v>
       </c>
       <c r="M30" t="n">
-        <v>2.66</v>
+        <v>0.55</v>
       </c>
       <c r="N30" t="n">
-        <v>26637109</v>
+        <v>5545000</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>26637109</v>
+        <v>5545000</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -7389,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -7397,52 +7399,52 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.28</v>
+        <v>0.199</v>
       </c>
       <c r="W30" t="n">
-        <v>951</v>
+        <v>278</v>
       </c>
       <c r="X30" t="n">
-        <v>25.9</v>
+        <v>14.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.68</v>
+        <v>2.79</v>
       </c>
       <c r="AA30" t="n">
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.85</v>
+        <v>0.21</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.83</v>
+        <v>18</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.26</v>
+        <v>0.32</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>4.02</v>
+        <v>1.83</v>
       </c>
       <c r="AG30" t="n">
-        <v>88.90000000000001</v>
+        <v>27.98</v>
       </c>
       <c r="AH30" t="n">
-        <v>100.89</v>
+        <v>31.94</v>
       </c>
       <c r="AI30" t="n">
-        <v>14</v>
+        <v>5.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>96.1260636723853</v>
+        <v>27.725</v>
       </c>
       <c r="AK30" t="n">
-        <v>-3.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
@@ -7461,7 +7463,7 @@
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
@@ -7470,43 +7472,43 @@
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="AR30" t="n">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="AS30" t="n">
         <v>2</v>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY30" t="n">
-        <v>6202680</v>
+        <v>1331000</v>
       </c>
       <c r="AZ30" t="n">
-        <v>26023230</v>
+        <v>2651250</v>
       </c>
       <c r="BA30" t="n">
-        <v>26023230</v>
+        <v>3342250</v>
       </c>
       <c r="BB30" t="n">
-        <v>26023230</v>
+        <v>5545000</v>
       </c>
       <c r="BC30" t="n">
-        <v>26023230</v>
+        <v>5545000</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
@@ -7539,10 +7541,10 @@
         <v>0</v>
       </c>
       <c r="BN30" t="n">
-        <v>6202680</v>
+        <v>1331000</v>
       </c>
       <c r="BO30" t="n">
-        <v>26023230</v>
+        <v>3342250</v>
       </c>
       <c r="BP30" t="n">
         <v>1</v>
@@ -7551,22 +7553,22 @@
         <v>0</v>
       </c>
       <c r="BR30" t="n">
-        <v>0.2384</v>
+        <v>0.3982</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7574,107 +7576,101 @@
         </is>
       </c>
       <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="G31" t="n">
+        <v>13</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L31" t="n">
+        <v>64.45</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N31" t="n">
+        <v>20159573</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>20159573</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>24-09-2026</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
         <v>10</v>
       </c>
-      <c r="F31" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>171.1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>174.27</v>
-      </c>
-      <c r="K31" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="L31" t="n">
-        <v>61.48</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N31" t="n">
-        <v>10743104</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>10743104</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S31" t="b">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>7</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>0.491</v>
-      </c>
-      <c r="W31" t="n">
-        <v>219</v>
-      </c>
-      <c r="X31" t="n">
-        <v>38</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>-44</v>
-      </c>
       <c r="Z31" t="n">
-        <v>-3.28</v>
+        <v>0.98</v>
       </c>
       <c r="AA31" t="n">
-        <v>141</v>
+        <v>-86</v>
       </c>
       <c r="AB31" t="n">
-        <v>-4.05</v>
+        <v>-0.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>8.25</v>
+        <v>2.27</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE31" t="b">
         <v>1</v>
       </c>
       <c r="AF31" t="n">
-        <v>-35.96</v>
+        <v>14.22</v>
       </c>
       <c r="AG31" t="n">
-        <v>173.05</v>
+        <v>2.89</v>
       </c>
       <c r="AH31" t="n">
-        <v>178.42</v>
+        <v>3.18</v>
       </c>
       <c r="AI31" t="n">
-        <v>30.1</v>
+        <v>10.6</v>
       </c>
       <c r="AJ31" t="n">
-        <v>174.2652478588113</v>
+        <v>2.817550384346611</v>
       </c>
       <c r="AK31" t="n">
-        <v>-1.8</v>
+        <v>3.6</v>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
@@ -7693,7 +7689,7 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
@@ -7702,10 +7698,10 @@
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -7714,31 +7710,31 @@
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AX31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>9361398</v>
+        <v>20159573</v>
       </c>
       <c r="BA31" t="n">
-        <v>10743104</v>
+        <v>20159573</v>
       </c>
       <c r="BB31" t="n">
-        <v>10743104</v>
+        <v>20159573</v>
       </c>
       <c r="BC31" t="n">
-        <v>10743104</v>
+        <v>20159573</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
@@ -7774,7 +7770,7 @@
         <v>0</v>
       </c>
       <c r="BO31" t="n">
-        <v>10743104</v>
+        <v>20159573</v>
       </c>
       <c r="BP31" t="n">
         <v>1</v>
@@ -7789,16 +7785,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7806,40 +7802,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>-2</v>
+        <v>16</v>
       </c>
       <c r="G32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2.92</v>
+        <v>393.85</v>
       </c>
       <c r="J32" t="n">
-        <v>2.82</v>
+        <v>417.34</v>
       </c>
       <c r="K32" t="n">
-        <v>3.5</v>
+        <v>-5.6</v>
       </c>
       <c r="L32" t="n">
-        <v>64.45</v>
+        <v>61.75</v>
       </c>
       <c r="M32" t="n">
-        <v>2.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>20159573</v>
+        <v>6931636</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>20159573</v>
+        <v>6931636</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -7857,90 +7853,96 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1550</v>
+      </c>
+      <c r="X32" t="n">
+        <v>20.2</v>
+      </c>
       <c r="Y32" t="n">
         <v>10</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.98</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="n">
-        <v>-86</v>
+        <v>2</v>
       </c>
       <c r="AB32" t="n">
-        <v>-0.03</v>
+        <v>3.37</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.27</v>
+        <v>23.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.58</v>
+        <v>0.01</v>
       </c>
       <c r="AE32" t="b">
         <v>1</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.22</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.89</v>
+        <v>431.27</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.18</v>
+        <v>476.81</v>
       </c>
       <c r="AI32" t="n">
-        <v>10.6</v>
+        <v>-15.2</v>
       </c>
       <c r="AJ32" t="n">
-        <v>2.817550384346611</v>
+        <v>417.3421638870492</v>
       </c>
       <c r="AK32" t="n">
-        <v>3.6</v>
+        <v>-5.6</v>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AS32" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
         <v>1</v>
@@ -7955,16 +7957,16 @@
         <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>20159573</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>20159573</v>
+        <v>6931636</v>
       </c>
       <c r="BB32" t="n">
-        <v>20159573</v>
+        <v>6931636</v>
       </c>
       <c r="BC32" t="n">
-        <v>20159573</v>
+        <v>6931636</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
@@ -8000,7 +8002,7 @@
         <v>0</v>
       </c>
       <c r="BO32" t="n">
-        <v>20159573</v>
+        <v>6931636</v>
       </c>
       <c r="BP32" t="n">
         <v>1</v>
@@ -8015,16 +8017,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -8032,107 +8034,107 @@
         </is>
       </c>
       <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>19</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>151.41</v>
+      </c>
+      <c r="J33" t="n">
+        <v>176.53</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-14.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>64.08</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N33" t="n">
+        <v>13998476</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>13998476</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
-        <v>16</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>393.85</v>
-      </c>
-      <c r="J33" t="n">
-        <v>417.34</v>
-      </c>
-      <c r="K33" t="n">
-        <v>-5.6</v>
-      </c>
-      <c r="L33" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="N33" t="n">
-        <v>6931636</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>6931636</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S33" t="b">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1</v>
-      </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V33" t="n">
-        <v>0.045</v>
+        <v>0.229</v>
       </c>
       <c r="W33" t="n">
-        <v>1549</v>
+        <v>612</v>
       </c>
       <c r="X33" t="n">
-        <v>20.2</v>
+        <v>13.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>10</v>
+        <v>-1</v>
       </c>
       <c r="Z33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>23.3</v>
+        <v>19.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE33" t="b">
         <v>1</v>
       </c>
       <c r="AF33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG33" t="n">
-        <v>431.27</v>
+        <v>166.25</v>
       </c>
       <c r="AH33" t="n">
-        <v>476.81</v>
+        <v>189.19</v>
       </c>
       <c r="AI33" t="n">
-        <v>-15.2</v>
+        <v>-9</v>
       </c>
       <c r="AJ33" t="n">
-        <v>417.3421638870492</v>
+        <v>176.5255485498108</v>
       </c>
       <c r="AK33" t="n">
-        <v>-5.6</v>
+        <v>-14.2</v>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
@@ -8141,7 +8143,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
@@ -8151,22 +8153,22 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AR33" t="n">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="AS33" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AT33" t="n">
         <v>0</v>
@@ -8178,10 +8180,10 @@
         <v>1</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -8190,13 +8192,13 @@
         <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>6931636</v>
+        <v>3009963</v>
       </c>
       <c r="BB33" t="n">
-        <v>6931636</v>
+        <v>8001009</v>
       </c>
       <c r="BC33" t="n">
-        <v>6931636</v>
+        <v>8001009</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
@@ -8232,7 +8234,7 @@
         <v>0</v>
       </c>
       <c r="BO33" t="n">
-        <v>6931636</v>
+        <v>3009963</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
@@ -8247,16 +8249,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -8264,171 +8266,171 @@
         </is>
       </c>
       <c r="E34" t="n">
+        <v>11</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>25</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-16</v>
+      </c>
+      <c r="I34" t="n">
+        <v>468.65</v>
+      </c>
+      <c r="J34" t="n">
+        <v>349.57</v>
+      </c>
+      <c r="K34" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>70.55</v>
+      </c>
+      <c r="M34" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N34" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>315995536</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>11</v>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4019</v>
+      </c>
+      <c r="X34" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>127</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-14</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>441.05</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>432.49</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>349.5746258337085</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ34" t="n">
+        <v>56</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>57</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU34" t="n">
         <v>4</v>
       </c>
-      <c r="F34" t="n">
-        <v>19</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>151.41</v>
-      </c>
-      <c r="J34" t="n">
-        <v>176.53</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>64.08</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N34" t="n">
-        <v>13998476</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>13998476</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S34" t="b">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>3</v>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="V34" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="W34" t="n">
-        <v>611</v>
-      </c>
-      <c r="X34" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>45</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="AE34" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF34" t="n">
+      <c r="AV34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW34" t="n">
         <v>11</v>
       </c>
-      <c r="AG34" t="n">
-        <v>166.25</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>189.19</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>176.5255485498108</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>-14.2</v>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="AP34" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ34" t="n">
-        <v>64</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>93</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>2</v>
-      </c>
       <c r="AX34" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>122602303</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>143834303</v>
       </c>
       <c r="BA34" t="n">
-        <v>3009963</v>
+        <v>213764633</v>
       </c>
       <c r="BB34" t="n">
-        <v>8001009</v>
+        <v>315995536</v>
       </c>
       <c r="BC34" t="n">
-        <v>8001009</v>
+        <v>315995536</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
@@ -8461,10 +8463,10 @@
         <v>0</v>
       </c>
       <c r="BN34" t="n">
-        <v>0</v>
+        <v>122602303</v>
       </c>
       <c r="BO34" t="n">
-        <v>3009963</v>
+        <v>213764633</v>
       </c>
       <c r="BP34" t="n">
         <v>1</v>
@@ -8473,22 +8475,22 @@
         <v>0</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>0.5735</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -8496,171 +8498,171 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F35" t="n">
+        <v>5</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>156.18</v>
+      </c>
+      <c r="J35" t="n">
+        <v>159.62</v>
+      </c>
+      <c r="K35" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L35" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="N35" t="n">
+        <v>39906048</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>39906048</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1734</v>
+      </c>
+      <c r="X35" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="Y35" t="n">
         <v>-3</v>
       </c>
-      <c r="G35" t="n">
-        <v>25</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-16</v>
-      </c>
-      <c r="I35" t="n">
-        <v>468.65</v>
-      </c>
-      <c r="J35" t="n">
-        <v>349.57</v>
-      </c>
-      <c r="K35" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="L35" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="M35" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
-      <c r="P35" t="n">
-        <v>315995536</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S35" t="b">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>11</v>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="V35" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="W35" t="n">
-        <v>4019</v>
-      </c>
-      <c r="X35" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="Y35" t="n">
+      <c r="Z35" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>175.81</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>184.76</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>-10.1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>159.624192</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AL35" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>16-09-2026</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>17-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
         <v>2</v>
       </c>
-      <c r="Z35" t="n">
-        <v>127</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>-14</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>441.05</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>432.49</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>349.5746258337085</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AP35" t="inlineStr">
-        <is>
-          <t>30-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ35" t="n">
-        <v>56</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>57</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>6</v>
-      </c>
       <c r="AW35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AX35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AY35" t="n">
-        <v>122602303</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>143834303</v>
+        <v>7834435</v>
       </c>
       <c r="BA35" t="n">
-        <v>213764633</v>
+        <v>39906048</v>
       </c>
       <c r="BB35" t="n">
-        <v>315995536</v>
+        <v>39906048</v>
       </c>
       <c r="BC35" t="n">
-        <v>315995536</v>
+        <v>39906048</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
@@ -8693,10 +8695,10 @@
         <v>0</v>
       </c>
       <c r="BN35" t="n">
-        <v>122602303</v>
+        <v>0</v>
       </c>
       <c r="BO35" t="n">
-        <v>213764633</v>
+        <v>39906048</v>
       </c>
       <c r="BP35" t="n">
         <v>1</v>
@@ -8705,18 +8707,18 @@
         <v>0</v>
       </c>
       <c r="BR35" t="n">
-        <v>0.5735</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -8728,40 +8730,40 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I36" t="n">
-        <v>156.18</v>
+        <v>39.42</v>
       </c>
       <c r="J36" t="n">
-        <v>159.62</v>
+        <v>42.6</v>
       </c>
       <c r="K36" t="n">
-        <v>-2.2</v>
+        <v>-7.5</v>
       </c>
       <c r="L36" t="n">
-        <v>65.64</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>3.99</v>
+        <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>39906048</v>
+        <v>13998766</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>39906048</v>
+        <v>13998766</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -8775,60 +8777,60 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.231</v>
+        <v>0.359</v>
       </c>
       <c r="W36" t="n">
-        <v>1727</v>
+        <v>390</v>
       </c>
       <c r="X36" t="n">
-        <v>18.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="Y36" t="n">
-        <v>-3</v>
+        <v>246</v>
       </c>
       <c r="Z36" t="n">
-        <v>26</v>
+        <v>0.91</v>
       </c>
       <c r="AA36" t="n">
-        <v>-4</v>
+        <v>10</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.36</v>
+        <v>0.14</v>
       </c>
       <c r="AC36" t="n">
-        <v>14.2</v>
+        <v>2.07</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>36</v>
+        <v>4.21</v>
       </c>
       <c r="AG36" t="n">
-        <v>175.81</v>
+        <v>40.58</v>
       </c>
       <c r="AH36" t="n">
-        <v>184.76</v>
+        <v>39.8</v>
       </c>
       <c r="AI36" t="n">
-        <v>-10.1</v>
+        <v>3.4</v>
       </c>
       <c r="AJ36" t="n">
-        <v>159.624192</v>
+        <v>42.60032805144139</v>
       </c>
       <c r="AK36" t="n">
-        <v>-2.2</v>
+        <v>-7.5</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -8847,52 +8849,52 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AR36" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="AS36" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
         <v>2</v>
       </c>
       <c r="AW36" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AX36" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AY36" t="n">
         <v>0</v>
       </c>
       <c r="AZ36" t="n">
-        <v>7834435</v>
+        <v>0</v>
       </c>
       <c r="BA36" t="n">
-        <v>39906048</v>
+        <v>2062168</v>
       </c>
       <c r="BB36" t="n">
-        <v>39906048</v>
+        <v>13998766</v>
       </c>
       <c r="BC36" t="n">
-        <v>39906048</v>
+        <v>13998766</v>
       </c>
       <c r="BD36" t="n">
         <v>0</v>
@@ -8928,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="BO36" t="n">
-        <v>39906048</v>
+        <v>2062168</v>
       </c>
       <c r="BP36" t="n">
         <v>1</v>
@@ -8943,16 +8945,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>Maharashtra Seamless Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -8960,141 +8962,141 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="F37" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G37" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="H37" t="n">
-        <v>-2</v>
+        <v>-13</v>
       </c>
       <c r="I37" t="n">
-        <v>39.42</v>
+        <v>737.65</v>
       </c>
       <c r="J37" t="n">
-        <v>42.6</v>
+        <v>618.78</v>
       </c>
       <c r="K37" t="n">
-        <v>-7.5</v>
+        <v>19.2</v>
       </c>
       <c r="L37" t="n">
-        <v>71.79000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>102.7</v>
       </c>
       <c r="N37" t="n">
-        <v>13998766</v>
+        <v>1026988804</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1007459825</v>
       </c>
       <c r="P37" t="n">
-        <v>13998766</v>
+        <v>19528979</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Buying with Selling</t>
         </is>
       </c>
       <c r="S37" t="b">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.36</v>
+        <v>0.02</v>
       </c>
       <c r="W37" t="n">
-        <v>389</v>
+        <v>9884</v>
       </c>
       <c r="X37" t="n">
-        <v>96.40000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="Y37" t="n">
-        <v>246</v>
+        <v>-12</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.91</v>
+        <v>184</v>
       </c>
       <c r="AA37" t="n">
-        <v>10</v>
+        <v>-15</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.14</v>
+        <v>20.21</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.07</v>
+        <v>13.8</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
-        <v>4.21</v>
+        <v>17</v>
       </c>
       <c r="AG37" t="n">
-        <v>40.58</v>
+        <v>643.84</v>
       </c>
       <c r="AH37" t="n">
-        <v>39.8</v>
+        <v>598.1900000000001</v>
       </c>
       <c r="AI37" t="n">
-        <v>3.4</v>
+        <v>30.9</v>
       </c>
       <c r="AJ37" t="n">
-        <v>42.60032805144139</v>
+        <v>618.7797818882931</v>
       </c>
       <c r="AK37" t="n">
-        <v>-7.5</v>
+        <v>19.2</v>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
       <c r="AQ37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="AS37" t="n">
-        <v>29</v>
+        <v>93</v>
       </c>
       <c r="AT37" t="n">
         <v>0</v>
@@ -9103,13 +9105,13 @@
         <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
         <v>0</v>
@@ -9118,13 +9120,13 @@
         <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2062168</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>13998766</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>13998766</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
         <v>0</v>
@@ -9160,13 +9162,13 @@
         <v>0</v>
       </c>
       <c r="BO37" t="n">
-        <v>2062168</v>
+        <v>0</v>
       </c>
       <c r="BP37" t="n">
         <v>1</v>
       </c>
       <c r="BQ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR37" t="n">
         <v>0</v>
@@ -9175,16 +9177,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Maharashtra Seamless Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -9192,156 +9194,156 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="n">
         <v>9</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>189.62</v>
+      </c>
+      <c r="J38" t="n">
+        <v>191.87</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L38" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="N38" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>13430794</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="W38" t="n">
+        <v>3328</v>
+      </c>
+      <c r="X38" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>-4</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
         <v>21</v>
       </c>
-      <c r="H38" t="n">
-        <v>-13</v>
-      </c>
-      <c r="I38" t="n">
-        <v>737.65</v>
-      </c>
-      <c r="J38" t="n">
-        <v>618.78</v>
-      </c>
-      <c r="K38" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="L38" t="n">
-        <v>67.86</v>
-      </c>
-      <c r="M38" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1026988804</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1007459825</v>
-      </c>
-      <c r="P38" t="n">
-        <v>19528979</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>Net Buying with Selling</t>
-        </is>
-      </c>
-      <c r="S38" t="b">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
+      <c r="AG38" t="n">
+        <v>204.4</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>191.8684857142857</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="AL38" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>31</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>1</v>
       </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="V38" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="W38" t="n">
-        <v>9903</v>
-      </c>
-      <c r="X38" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>-12</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>184</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>-15</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>20.21</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>17</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>643.84</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>598.1900000000001</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>618.7797818882931</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="AP38" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>93</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>93</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY38" t="n">
         <v>0</v>
@@ -9350,13 +9352,13 @@
         <v>0</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>4274878</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="BD38" t="n">
         <v>0</v>
@@ -9392,13 +9394,13 @@
         <v>0</v>
       </c>
       <c r="BO38" t="n">
-        <v>0</v>
+        <v>4274878</v>
       </c>
       <c r="BP38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR38" t="n">
         <v>0</v>
@@ -9407,354 +9409,354 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>43</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Watchlist</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>16</v>
+      </c>
+      <c r="G39" t="n">
+        <v>21</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>196.38</v>
+      </c>
+      <c r="J39" t="n">
+        <v>195.05</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L39" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Net Buying</t>
+        </is>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="W39" t="n">
+        <v>4163</v>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>39</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>258</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>188.86</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>176.64</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>195.0500869565217</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AL39" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>22-09-2026</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ39" t="n">
         <v>3</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>3</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="AR39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT39" t="n">
         <v>1</v>
       </c>
-      <c r="G39" t="n">
-        <v>9</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>189.62</v>
-      </c>
-      <c r="J39" t="n">
-        <v>191.87</v>
-      </c>
-      <c r="K39" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>70.02</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="N39" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S39" t="b">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3330</v>
-      </c>
-      <c r="X39" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>-4</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>51</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>-9</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AE39" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>204.4</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>193.5</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>37.4</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>191.8684857142857</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="AP39" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>31</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1603718</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>1603718</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>4486152</v>
+      </c>
+      <c r="BP39" t="n">
         <v>1</v>
       </c>
-      <c r="AW39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>4274878</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>13430794</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>4274878</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ39" t="n">
         <v>0</v>
       </c>
       <c r="BR39" t="n">
-        <v>0</v>
+        <v>0.3575</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Savita Oil Technologies Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="I40" t="n">
-        <v>196.38</v>
+        <v>718.8</v>
       </c>
       <c r="J40" t="n">
-        <v>195.05</v>
+        <v>726.25</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
       <c r="L40" t="n">
-        <v>60.6</v>
+        <v>71.92</v>
       </c>
       <c r="M40" t="n">
-        <v>0.45</v>
+        <v>3.76</v>
       </c>
       <c r="N40" t="n">
-        <v>4486152</v>
+        <v>37641643</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="P40" t="n">
-        <v>4486152</v>
+        <v>214003</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Buying with Selling</t>
         </is>
       </c>
       <c r="S40" t="b">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="V40" t="n">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>4169</v>
-      </c>
-      <c r="X40" t="inlineStr"/>
+        <v>4928</v>
+      </c>
+      <c r="X40" t="n">
+        <v>11.5</v>
+      </c>
       <c r="Y40" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="Z40" t="n">
-        <v>258</v>
+        <v>364</v>
       </c>
       <c r="AA40" t="n">
-        <v>30</v>
+        <v>204</v>
       </c>
       <c r="AB40" t="n">
-        <v>-1.13</v>
+        <v>42.63</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.38</v>
+        <v>14</v>
       </c>
       <c r="AD40" t="n">
-        <v>10.11</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>1</v>
       </c>
       <c r="AF40" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="AG40" t="n">
-        <v>188.86</v>
+        <v>690.3</v>
       </c>
       <c r="AH40" t="n">
-        <v>176.64</v>
+        <v>482.38</v>
       </c>
       <c r="AI40" t="n">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="AJ40" t="n">
-        <v>195.0500869565217</v>
+        <v>726.2520355006753</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
       <c r="AL40" t="inlineStr">
         <is>
@@ -9773,112 +9775,112 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
       <c r="AQ40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>1603718</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>4486152</v>
+        <v>37641643</v>
       </c>
       <c r="BA40" t="n">
-        <v>4486152</v>
+        <v>37641643</v>
       </c>
       <c r="BB40" t="n">
-        <v>4486152</v>
+        <v>37641643</v>
       </c>
       <c r="BC40" t="n">
-        <v>4486152</v>
+        <v>37641643</v>
       </c>
       <c r="BD40" t="n">
         <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BH40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BI40" t="n">
         <v>0</v>
       </c>
       <c r="BJ40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BK40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BL40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BM40" t="n">
-        <v>0</v>
+        <v>37427640</v>
       </c>
       <c r="BN40" t="n">
-        <v>1603718</v>
+        <v>0</v>
       </c>
       <c r="BO40" t="n">
-        <v>4486152</v>
+        <v>214003</v>
       </c>
       <c r="BP40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR40" t="n">
-        <v>0.3575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Savita Oil Technologies Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -9886,47 +9888,47 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="G41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H41" t="n">
-        <v>-13</v>
+        <v>-1</v>
       </c>
       <c r="I41" t="n">
-        <v>718.8</v>
+        <v>182.73</v>
       </c>
       <c r="J41" t="n">
-        <v>726.25</v>
+        <v>170.45</v>
       </c>
       <c r="K41" t="n">
-        <v>-1</v>
+        <v>7.2</v>
       </c>
       <c r="L41" t="n">
-        <v>71.92</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>3.76</v>
+        <v>0.26</v>
       </c>
       <c r="N41" t="n">
-        <v>37641643</v>
+        <v>2560187</v>
       </c>
       <c r="O41" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>214003</v>
+        <v>2560187</v>
       </c>
       <c r="Q41" t="n">
-        <v>99.43000000000001</v>
+        <v>0</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Net Buying with Selling</t>
+          <t>Net Buying</t>
         </is>
       </c>
       <c r="S41" t="b">
@@ -9937,32 +9939,32 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.104</v>
       </c>
       <c r="W41" t="n">
-        <v>4914</v>
+        <v>246</v>
       </c>
       <c r="X41" t="n">
-        <v>11.5</v>
+        <v>26.3</v>
       </c>
       <c r="Y41" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z41" t="n">
-        <v>364</v>
+        <v>1.87</v>
       </c>
       <c r="AA41" t="n">
-        <v>204</v>
+        <v>-31</v>
       </c>
       <c r="AB41" t="n">
-        <v>42.63</v>
+        <v>3.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>14</v>
+        <v>4.96</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -9971,62 +9973,62 @@
         <v>1</v>
       </c>
       <c r="AF41" t="n">
-        <v>25</v>
+        <v>2.97</v>
       </c>
       <c r="AG41" t="n">
-        <v>690.3</v>
+        <v>181.35</v>
       </c>
       <c r="AH41" t="n">
-        <v>482.38</v>
+        <v>164.14</v>
       </c>
       <c r="AI41" t="n">
-        <v>139</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AJ41" t="n">
-        <v>726.2520355006753</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AK41" t="n">
-        <v>-1</v>
+        <v>7.2</v>
       </c>
       <c r="AL41" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ41" t="n">
         <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AS41" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV41" t="n">
         <v>2</v>
@@ -10041,58 +10043,58 @@
         <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>37641643</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>37641643</v>
+        <v>2560187</v>
       </c>
       <c r="BB41" t="n">
-        <v>37641643</v>
+        <v>2560187</v>
       </c>
       <c r="BC41" t="n">
-        <v>37641643</v>
+        <v>2560187</v>
       </c>
       <c r="BD41" t="n">
         <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BH41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BI41" t="n">
         <v>0</v>
       </c>
       <c r="BJ41" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BK41" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BL41" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BM41" t="n">
-        <v>37427640</v>
+        <v>0</v>
       </c>
       <c r="BN41" t="n">
         <v>0</v>
       </c>
       <c r="BO41" t="n">
-        <v>214003</v>
+        <v>2560187</v>
       </c>
       <c r="BP41" t="n">
         <v>2</v>
       </c>
       <c r="BQ41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR41" t="n">
         <v>0</v>
@@ -10101,16 +10103,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -10118,40 +10120,40 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G42" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H42" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>182.73</v>
+        <v>21.8</v>
       </c>
       <c r="J42" t="n">
-        <v>170.45</v>
+        <v>21.01</v>
       </c>
       <c r="K42" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="L42" t="n">
-        <v>67.54000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="M42" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="N42" t="n">
-        <v>2560187</v>
+        <v>4960333</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2560187</v>
+        <v>4960333</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -10165,163 +10167,159 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W42" t="n">
+        <v>415</v>
+      </c>
+      <c r="X42" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>118</v>
+      </c>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="n">
+        <v>391</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="n">
+        <v>19.74</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>21.00741139152052</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AL42" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>Mature — Wait for Pullback</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AP42" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="AQ42" t="n">
         <v>2</v>
       </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="V42" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="W42" t="n">
-        <v>244</v>
-      </c>
-      <c r="X42" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>-31</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="b">
+      <c r="AR42" t="n">
+        <v>45</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>4960333</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>4960333</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP42" t="n">
         <v>1</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>181.35</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>164.14</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>170.4518641810919</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AP42" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>2560187</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>2560187</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2560187</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO42" t="n">
-        <v>2560187</v>
-      </c>
-      <c r="BP42" t="n">
-        <v>2</v>
       </c>
       <c r="BQ42" t="n">
         <v>0</v>
@@ -10333,27 +10331,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G43" t="n">
         <v>21</v>
@@ -10362,28 +10360,28 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>21.8</v>
+        <v>389.15</v>
       </c>
       <c r="J43" t="n">
-        <v>21.01</v>
+        <v>338.1</v>
       </c>
       <c r="K43" t="n">
-        <v>3.8</v>
+        <v>15.1</v>
       </c>
       <c r="L43" t="n">
-        <v>70.87</v>
+        <v>66.73</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="N43" t="n">
-        <v>4960333</v>
+        <v>3381000</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>4960333</v>
+        <v>3381000</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -10397,56 +10395,60 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.12</v>
+        <v>0.074</v>
       </c>
       <c r="W43" t="n">
-        <v>413</v>
+        <v>459</v>
       </c>
       <c r="X43" t="n">
-        <v>6.66</v>
+        <v>13.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>118</v>
-      </c>
-      <c r="Z43" t="inlineStr"/>
+        <v>-8</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>24</v>
+      </c>
       <c r="AA43" t="n">
-        <v>391</v>
+        <v>33</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.03</v>
+        <v>14.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>19.9</v>
+        <v>9.94</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.01</v>
+        <v>0.23</v>
       </c>
       <c r="AE43" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>18</v>
+      </c>
       <c r="AG43" t="n">
-        <v>19.74</v>
+        <v>366.73</v>
       </c>
       <c r="AH43" t="n">
-        <v>15.58</v>
+        <v>272.07</v>
       </c>
       <c r="AI43" t="n">
-        <v>80.5</v>
+        <v>99.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>21.00741139152052</v>
+        <v>338.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>3.8</v>
+        <v>15.1</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
@@ -10465,22 +10467,22 @@
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AS43" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AT43" t="n">
         <v>0</v>
@@ -10492,10 +10494,10 @@
         <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
@@ -10507,10 +10509,10 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>4960333</v>
+        <v>3381000</v>
       </c>
       <c r="BC43" t="n">
-        <v>4960333</v>
+        <v>3381000</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
@@ -10561,16 +10563,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10578,40 +10580,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F44" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>389.15</v>
+        <v>35.05</v>
       </c>
       <c r="J44" t="n">
-        <v>338.1</v>
+        <v>23.55</v>
       </c>
       <c r="K44" t="n">
-        <v>15.1</v>
+        <v>48.8</v>
       </c>
       <c r="L44" t="n">
-        <v>66.73</v>
+        <v>68.34</v>
       </c>
       <c r="M44" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -10625,124 +10627,124 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.073</v>
+        <v>0.113</v>
       </c>
       <c r="W44" t="n">
-        <v>460</v>
+        <v>179</v>
       </c>
       <c r="X44" t="n">
-        <v>13.6</v>
+        <v>41.4</v>
       </c>
       <c r="Y44" t="n">
-        <v>-8</v>
+        <v>19</v>
       </c>
       <c r="Z44" t="n">
-        <v>24</v>
+        <v>3.17</v>
       </c>
       <c r="AA44" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="AB44" t="n">
-        <v>14.36</v>
+        <v>0.49</v>
       </c>
       <c r="AC44" t="n">
-        <v>9.94</v>
+        <v>8.76</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
       <c r="AE44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>18</v>
+        <v>14.87</v>
       </c>
       <c r="AG44" t="n">
-        <v>366.73</v>
+        <v>23.74</v>
       </c>
       <c r="AH44" t="n">
-        <v>272.07</v>
+        <v>22.79</v>
       </c>
       <c r="AI44" t="n">
-        <v>99.5</v>
+        <v>92.8</v>
       </c>
       <c r="AJ44" t="n">
-        <v>338.1</v>
+        <v>23.5472893358377</v>
       </c>
       <c r="AK44" t="n">
-        <v>15.1</v>
+        <v>48.8</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AR44" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="AS44" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW44" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AX44" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1188529</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>1457700</v>
       </c>
       <c r="BB44" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="BC44" t="n">
-        <v>3381000</v>
+        <v>2018403</v>
       </c>
       <c r="BD44" t="n">
         <v>0</v>
@@ -10778,10 +10780,10 @@
         <v>0</v>
       </c>
       <c r="BO44" t="n">
-        <v>0</v>
+        <v>1457700</v>
       </c>
       <c r="BP44" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BQ44" t="n">
         <v>0</v>
@@ -10793,16 +10795,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10810,10 +10812,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="G45" t="n">
         <v>25</v>
@@ -10822,28 +10824,28 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>35.05</v>
+        <v>666.2</v>
       </c>
       <c r="J45" t="n">
-        <v>23.55</v>
+        <v>593.62</v>
       </c>
       <c r="K45" t="n">
-        <v>48.8</v>
+        <v>12.2</v>
       </c>
       <c r="L45" t="n">
-        <v>68.34</v>
+        <v>74.02</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="N45" t="n">
-        <v>2018403</v>
+        <v>2458195</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2018403</v>
+        <v>2458195</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -10857,60 +10859,58 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.113</v>
+        <v>0.024</v>
       </c>
       <c r="W45" t="n">
-        <v>179</v>
-      </c>
-      <c r="X45" t="n">
-        <v>41.4</v>
-      </c>
+        <v>1035</v>
+      </c>
+      <c r="X45" t="inlineStr"/>
       <c r="Y45" t="n">
-        <v>19</v>
+        <v>-2</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.17</v>
+        <v>5</v>
       </c>
       <c r="AA45" t="n">
-        <v>7</v>
+        <v>-152</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.49</v>
+        <v>-6.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>8.76</v>
+        <v>9.24</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.2</v>
+        <v>2.23</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF45" t="n">
-        <v>14.87</v>
+        <v>6</v>
       </c>
       <c r="AG45" t="n">
-        <v>23.74</v>
+        <v>598.4</v>
       </c>
       <c r="AH45" t="n">
-        <v>22.79</v>
+        <v>549.58</v>
       </c>
       <c r="AI45" t="n">
-        <v>92.8</v>
+        <v>36.6</v>
       </c>
       <c r="AJ45" t="n">
-        <v>23.5472893358377</v>
+        <v>593.6235208886742</v>
       </c>
       <c r="AK45" t="n">
-        <v>48.8</v>
+        <v>12.2</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -10924,57 +10924,57 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="AQ45" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR45" t="n">
         <v>34</v>
       </c>
-      <c r="AR45" t="n">
-        <v>42</v>
-      </c>
       <c r="AS45" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="AW45" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AX45" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>1188529</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="n">
-        <v>1457700</v>
+        <v>1288195</v>
       </c>
       <c r="BB45" t="n">
-        <v>2018403</v>
+        <v>2458195</v>
       </c>
       <c r="BC45" t="n">
-        <v>2018403</v>
+        <v>2458195</v>
       </c>
       <c r="BD45" t="n">
         <v>0</v>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="BO45" t="n">
-        <v>1457700</v>
+        <v>1288195</v>
       </c>
       <c r="BP45" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BQ45" t="n">
         <v>0</v>
@@ -11025,16 +11025,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -11042,40 +11042,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>-5</v>
+        <v>15</v>
       </c>
       <c r="G46" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>666.2</v>
+        <v>320.95</v>
       </c>
       <c r="J46" t="n">
-        <v>593.62</v>
+        <v>335.41</v>
       </c>
       <c r="K46" t="n">
-        <v>12.2</v>
+        <v>-4.3</v>
       </c>
       <c r="L46" t="n">
-        <v>74.02</v>
+        <v>68.48</v>
       </c>
       <c r="M46" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="N46" t="n">
-        <v>2458195</v>
+        <v>4081958</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>2458195</v>
+        <v>4081958</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
@@ -11089,107 +11089,109 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="V46" t="n">
-        <v>0.024</v>
+        <v>0.008</v>
       </c>
       <c r="W46" t="n">
-        <v>1039</v>
-      </c>
-      <c r="X46" t="inlineStr"/>
+        <v>5260</v>
+      </c>
+      <c r="X46" t="n">
+        <v>8.890000000000001</v>
+      </c>
       <c r="Y46" t="n">
-        <v>-2</v>
+        <v>43</v>
       </c>
       <c r="Z46" t="n">
-        <v>5</v>
+        <v>223</v>
       </c>
       <c r="AA46" t="n">
-        <v>-152</v>
+        <v>175</v>
       </c>
       <c r="AB46" t="n">
-        <v>-6.5</v>
+        <v>6.97</v>
       </c>
       <c r="AC46" t="n">
-        <v>9.24</v>
+        <v>21.4</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.23</v>
+        <v>1.03</v>
       </c>
       <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>361.65</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>335.78</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>335.4115036976171</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="AL46" t="inlineStr">
+        <is>
+          <t>Aging</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Mature Accumulation</t>
+        </is>
+      </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>Mature — Wait for Pullback</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="AP46" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="AQ46" t="n">
+        <v>49</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>93</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
         <v>1</v>
       </c>
-      <c r="AF46" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>598.4</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>549.58</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>593.6235208886742</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="AP46" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ46" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>3</v>
-      </c>
       <c r="AX46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
@@ -11198,13 +11200,13 @@
         <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>1288195</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>2458195</v>
+        <v>1094828</v>
       </c>
       <c r="BC46" t="n">
-        <v>2458195</v>
+        <v>1094828</v>
       </c>
       <c r="BD46" t="n">
         <v>0</v>
@@ -11240,10 +11242,10 @@
         <v>0</v>
       </c>
       <c r="BO46" t="n">
-        <v>1288195</v>
+        <v>0</v>
       </c>
       <c r="BP46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ46" t="n">
         <v>0</v>
@@ -11255,12 +11257,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>MAS Financial Services Limited</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -11272,40 +11274,40 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F47" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>320.95</v>
+        <v>282.7</v>
       </c>
       <c r="J47" t="n">
-        <v>335.41</v>
+        <v>278.98</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.3</v>
+        <v>1.3</v>
       </c>
       <c r="L47" t="n">
-        <v>68.48</v>
+        <v>73.72</v>
       </c>
       <c r="M47" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="N47" t="n">
-        <v>4081958</v>
+        <v>2789837</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>4081958</v>
+        <v>2789837</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -11323,120 +11325,116 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="W47" t="n">
-        <v>5264</v>
+        <v>5130</v>
       </c>
       <c r="X47" t="n">
-        <v>8.9</v>
+        <v>13.2</v>
       </c>
       <c r="Y47" t="n">
-        <v>43</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>223</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="Z47" t="inlineStr"/>
       <c r="AA47" t="n">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AB47" t="n">
-        <v>6.97</v>
+        <v>5.76</v>
       </c>
       <c r="AC47" t="n">
-        <v>21.4</v>
+        <v>11.3</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.03</v>
+        <v>3.31</v>
       </c>
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="n">
-        <v>7</v>
-      </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="n">
-        <v>361.65</v>
+        <v>299.52</v>
       </c>
       <c r="AH47" t="n">
-        <v>335.78</v>
+        <v>311.95</v>
       </c>
       <c r="AI47" t="n">
-        <v>12.5</v>
+        <v>-3.3</v>
       </c>
       <c r="AJ47" t="n">
-        <v>335.4115036976171</v>
+        <v>278.9837</v>
       </c>
       <c r="AK47" t="n">
-        <v>-4.3</v>
+        <v>1.3</v>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ47" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="AR47" t="n">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="AS47" t="n">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>2789837</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2789837</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2789837</v>
       </c>
       <c r="BB47" t="n">
-        <v>1094828</v>
+        <v>2789837</v>
       </c>
       <c r="BC47" t="n">
-        <v>1094828</v>
+        <v>2789837</v>
       </c>
       <c r="BD47" t="n">
         <v>0</v>
@@ -11469,10 +11467,10 @@
         <v>0</v>
       </c>
       <c r="BN47" t="n">
-        <v>0</v>
+        <v>2789837</v>
       </c>
       <c r="BO47" t="n">
-        <v>0</v>
+        <v>2789837</v>
       </c>
       <c r="BP47" t="n">
         <v>1</v>
@@ -11481,22 +11479,22 @@
         <v>0</v>
       </c>
       <c r="BR47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MASFIN</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MAS Financial Services Limited</t>
+          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -11504,167 +11502,171 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="F48" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="I48" t="n">
-        <v>282.7</v>
+        <v>182.18</v>
       </c>
       <c r="J48" t="n">
-        <v>278.98</v>
+        <v>207.63</v>
       </c>
       <c r="K48" t="n">
-        <v>1.3</v>
+        <v>-12.3</v>
       </c>
       <c r="L48" t="n">
-        <v>73.72</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="M48" t="n">
-        <v>0.28</v>
+        <v>4.7</v>
       </c>
       <c r="N48" t="n">
-        <v>2789837</v>
+        <v>46970458</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>46898837</v>
       </c>
       <c r="P48" t="n">
-        <v>2789837</v>
+        <v>71621</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>Net Buying</t>
+          <t>Net Buying with Selling</t>
         </is>
       </c>
       <c r="S48" t="b">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="V48" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>5090</v>
+        <v>8856</v>
       </c>
       <c r="X48" t="n">
-        <v>13.1</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="n">
-        <v>23</v>
-      </c>
-      <c r="Z48" t="inlineStr"/>
+        <v>21</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>224</v>
+      </c>
       <c r="AA48" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AB48" t="n">
-        <v>5.76</v>
+        <v>3.32</v>
       </c>
       <c r="AC48" t="n">
-        <v>11.3</v>
+        <v>24.2</v>
       </c>
       <c r="AD48" t="n">
-        <v>3.31</v>
+        <v>0.11</v>
       </c>
       <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>41</v>
+      </c>
       <c r="AG48" t="n">
-        <v>299.52</v>
+        <v>197.76</v>
       </c>
       <c r="AH48" t="n">
-        <v>311.95</v>
+        <v>208.87</v>
       </c>
       <c r="AI48" t="n">
-        <v>-3.3</v>
+        <v>1.8</v>
       </c>
       <c r="AJ48" t="n">
-        <v>278.9837</v>
+        <v>207.6336012165256</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.3</v>
+        <v>-12.3</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AQ48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="AS48" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="AT48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>2789837</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2789837</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>2789837</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>2789837</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>2789837</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
         <v>0</v>
@@ -11697,176 +11699,176 @@
         <v>0</v>
       </c>
       <c r="BN48" t="n">
-        <v>2789837</v>
+        <v>0</v>
       </c>
       <c r="BO48" t="n">
-        <v>2789837</v>
+        <v>0</v>
       </c>
       <c r="BP48" t="n">
         <v>1</v>
       </c>
       <c r="BQ48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>7</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>4</v>
+      </c>
+      <c r="F49" t="n">
+        <v>5</v>
+      </c>
+      <c r="G49" t="n">
         <v>9</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
         <v>-1</v>
       </c>
-      <c r="F49" t="n">
-        <v>26</v>
-      </c>
-      <c r="G49" t="n">
-        <v>5</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-13</v>
-      </c>
       <c r="I49" t="n">
-        <v>182.18</v>
+        <v>112.09</v>
       </c>
       <c r="J49" t="n">
-        <v>207.63</v>
+        <v>111.01</v>
       </c>
       <c r="K49" t="n">
-        <v>-12.3</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>74.26000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="M49" t="n">
-        <v>4.7</v>
+        <v>0.45</v>
       </c>
       <c r="N49" t="n">
-        <v>46970458</v>
+        <v>4484713</v>
       </c>
       <c r="O49" t="n">
-        <v>46898837</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>71621</v>
+        <v>4484713</v>
       </c>
       <c r="Q49" t="n">
-        <v>99.84999999999999</v>
+        <v>0</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>Net Buying with Selling</t>
+          <t>Net Buying</t>
         </is>
       </c>
       <c r="S49" t="b">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.211</v>
       </c>
       <c r="W49" t="n">
-        <v>8836</v>
+        <v>213</v>
       </c>
       <c r="X49" t="n">
-        <v>15</v>
+        <v>25.3</v>
       </c>
       <c r="Y49" t="n">
         <v>21</v>
       </c>
       <c r="Z49" t="n">
-        <v>224</v>
+        <v>12.07</v>
       </c>
       <c r="AA49" t="n">
-        <v>38</v>
+        <v>-29</v>
       </c>
       <c r="AB49" t="n">
-        <v>3.32</v>
+        <v>1.02</v>
       </c>
       <c r="AC49" t="n">
-        <v>24.2</v>
+        <v>7.92</v>
       </c>
       <c r="AD49" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
       <c r="AE49" t="b">
         <v>1</v>
       </c>
       <c r="AF49" t="n">
-        <v>41</v>
+        <v>4.11</v>
       </c>
       <c r="AG49" t="n">
-        <v>197.76</v>
+        <v>112.09</v>
       </c>
       <c r="AH49" t="n">
-        <v>208.87</v>
+        <v>118</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.8</v>
+        <v>6.5</v>
       </c>
       <c r="AJ49" t="n">
-        <v>207.6336012165256</v>
+        <v>111.0077475247525</v>
       </c>
       <c r="AK49" t="n">
-        <v>-12.3</v>
+        <v>1</v>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AR49" t="n">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="AS49" t="n">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="AT49" t="n">
         <v>0</v>
@@ -11875,13 +11877,13 @@
         <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY49" t="n">
         <v>0</v>
@@ -11890,13 +11892,13 @@
         <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>663085</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>4484713</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>4484713</v>
       </c>
       <c r="BD49" t="n">
         <v>0</v>
@@ -11932,13 +11934,13 @@
         <v>0</v>
       </c>
       <c r="BO49" t="n">
-        <v>0</v>
+        <v>663085</v>
       </c>
       <c r="BP49" t="n">
         <v>1</v>
       </c>
       <c r="BQ49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR49" t="n">
         <v>0</v>
@@ -11947,16 +11949,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -11964,213 +11966,213 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G50" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="H50" t="n">
-        <v>-1</v>
+        <v>-19</v>
       </c>
       <c r="I50" t="n">
-        <v>112.09</v>
+        <v>1764.8</v>
       </c>
       <c r="J50" t="n">
-        <v>111.01</v>
+        <v>789.9400000000001</v>
       </c>
       <c r="K50" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="L50" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="M50" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="N50" t="n">
+        <v>127606073</v>
+      </c>
+      <c r="O50" t="n">
+        <v>130033072</v>
+      </c>
+      <c r="P50" t="n">
+        <v>-2426999</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Net Selling</t>
+        </is>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>3682</v>
+      </c>
+      <c r="X50" t="n">
+        <v>82.90000000000001</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>1644.24</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>1390.11</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>789.9446136512771</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="AL50" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AP50" t="inlineStr">
+        <is>
+          <t>25-06-2026</t>
+        </is>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>98</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>98</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ50" t="n">
         <v>1</v>
-      </c>
-      <c r="L50" t="n">
-        <v>73.48</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N50" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>Net Buying</t>
-        </is>
-      </c>
-      <c r="S50" t="b">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>8</v>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="W50" t="n">
-        <v>209</v>
-      </c>
-      <c r="X50" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>-29</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="AD50" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="AE50" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>112.09</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>118</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>111.0077475247525</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="AP50" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ50" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>45</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>8</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>663085</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>4484713</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN50" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO50" t="n">
-        <v>663085</v>
-      </c>
-      <c r="BP50" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ50" t="n">
-        <v>0</v>
       </c>
       <c r="BR50" t="n">
         <v>0</v>
@@ -12179,16 +12181,16 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>JINDAL STEEL LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -12199,40 +12201,40 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G51" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="H51" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="I51" t="n">
-        <v>1764.8</v>
+        <v>1134.9</v>
       </c>
       <c r="J51" t="n">
-        <v>789.9400000000001</v>
+        <v>1157.18</v>
       </c>
       <c r="K51" t="n">
-        <v>123.4</v>
+        <v>-1.9</v>
       </c>
       <c r="L51" t="n">
-        <v>67.55</v>
+        <v>61.21</v>
       </c>
       <c r="M51" t="n">
-        <v>12.76</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="N51" t="n">
-        <v>127606073</v>
+        <v>92111332</v>
       </c>
       <c r="O51" t="n">
-        <v>130033072</v>
+        <v>108203920</v>
       </c>
       <c r="P51" t="n">
-        <v>-2426999</v>
+        <v>-16092588</v>
       </c>
       <c r="Q51" t="n">
-        <v>101.9</v>
+        <v>117.47</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -12243,94 +12245,94 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="V51" t="n">
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>3676</v>
+        <v>115770</v>
       </c>
       <c r="X51" t="n">
-        <v>82.7</v>
+        <v>33.3</v>
       </c>
       <c r="Y51" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="Z51" t="n">
-        <v>13</v>
+        <v>2224</v>
       </c>
       <c r="AA51" t="n">
-        <v>22</v>
+        <v>-28</v>
       </c>
       <c r="AB51" t="n">
-        <v>5.05</v>
+        <v>10.65</v>
       </c>
       <c r="AC51" t="n">
-        <v>19.9</v>
+        <v>10.8</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="AE51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF51" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="AG51" t="n">
-        <v>1644.24</v>
+        <v>1122.7</v>
       </c>
       <c r="AH51" t="n">
-        <v>1390.11</v>
+        <v>1135.42</v>
       </c>
       <c r="AI51" t="n">
-        <v>64.2</v>
+        <v>0.3</v>
       </c>
       <c r="AJ51" t="n">
-        <v>789.9446136512771</v>
+        <v>1157.177537688442</v>
       </c>
       <c r="AK51" t="n">
-        <v>123.4</v>
+        <v>-1.9</v>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AQ51" t="n">
         <v>0</v>
       </c>
       <c r="AR51" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="AS51" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="AT51" t="n">
         <v>0</v>
@@ -12339,13 +12341,13 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY51" t="n">
         <v>0</v>
@@ -12354,13 +12356,13 @@
         <v>0</v>
       </c>
       <c r="BA51" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BB51" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BC51" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BD51" t="n">
         <v>0</v>
@@ -12372,10 +12374,10 @@
         <v>0</v>
       </c>
       <c r="BG51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BH51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BI51" t="n">
         <v>0</v>
@@ -12387,256 +12389,24 @@
         <v>0</v>
       </c>
       <c r="BL51" t="n">
-        <v>0</v>
+        <v>108203920</v>
       </c>
       <c r="BM51" t="n">
-        <v>0</v>
+        <v>108203920</v>
       </c>
       <c r="BN51" t="n">
         <v>0</v>
       </c>
       <c r="BO51" t="n">
-        <v>0</v>
+        <v>92111332</v>
       </c>
       <c r="BP51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ51" t="n">
         <v>1</v>
       </c>
       <c r="BR51" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>JINDAL STEEL LIMITED</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>12</v>
-      </c>
-      <c r="G52" t="n">
-        <v>9</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I52" t="n">
-        <v>1134.9</v>
-      </c>
-      <c r="J52" t="n">
-        <v>1157.18</v>
-      </c>
-      <c r="K52" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="L52" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="M52" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="N52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="O52" t="n">
-        <v>108203920</v>
-      </c>
-      <c r="P52" t="n">
-        <v>-16092588</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>117.47</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Net Selling</t>
-        </is>
-      </c>
-      <c r="S52" t="b">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>115821</v>
-      </c>
-      <c r="X52" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>2224</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>-28</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF52" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>1122.7</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>1135.42</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>1157.177537688442</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AP52" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS52" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BB52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL52" t="n">
-        <v>108203920</v>
-      </c>
-      <c r="BM52" t="n">
-        <v>108203920</v>
-      </c>
-      <c r="BN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO52" t="n">
-        <v>92111332</v>
-      </c>
-      <c r="BP52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ52" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12651,7 +12421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12727,19 +12497,19 @@
         <v>88.13</v>
       </c>
       <c r="D2" t="n">
-        <v>75.77</v>
+        <v>76.3</v>
       </c>
       <c r="E2" t="n">
-        <v>16.3</v>
+        <v>15.5</v>
       </c>
       <c r="F2" t="n">
         <v>61.32</v>
       </c>
       <c r="G2" t="n">
-        <v>88.06</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -13625,101 +13395,101 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>704.35</v>
+        <v>93.16</v>
       </c>
       <c r="D28" t="n">
-        <v>782.6</v>
+        <v>96.03</v>
       </c>
       <c r="E28" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="F28" t="n">
-        <v>73.2</v>
+        <v>71.89</v>
       </c>
       <c r="G28" t="n">
-        <v>0.54</v>
+        <v>2.6</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>AFFORDABLE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.25</v>
+        <v>171.1</v>
       </c>
       <c r="D29" t="n">
-        <v>29.64</v>
+        <v>174.27</v>
       </c>
       <c r="E29" t="n">
-        <v>-11.4</v>
+        <v>-1.8</v>
       </c>
       <c r="F29" t="n">
-        <v>61.81</v>
+        <v>61.48</v>
       </c>
       <c r="G29" t="n">
-        <v>0.74</v>
+        <v>1.07</v>
       </c>
       <c r="H29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>93.16</v>
+        <v>26.25</v>
       </c>
       <c r="D30" t="n">
-        <v>96.13</v>
+        <v>27.72</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.1</v>
+        <v>-5.3</v>
       </c>
       <c r="F30" t="n">
-        <v>71.89</v>
+        <v>61.81</v>
       </c>
       <c r="G30" t="n">
-        <v>2.66</v>
+        <v>0.55</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -13730,31 +13500,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AFFORDABLE</t>
+          <t>DANGEE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AFFORDABLE ROBOTIC &amp; AUTOMATION LIMITED</t>
+          <t>Dangee Dums Limited</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>171.1</v>
+        <v>2.92</v>
       </c>
       <c r="D31" t="n">
-        <v>174.27</v>
+        <v>2.82</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.8</v>
+        <v>3.5</v>
       </c>
       <c r="F31" t="n">
-        <v>61.48</v>
+        <v>64.45</v>
       </c>
       <c r="G31" t="n">
-        <v>1.07</v>
+        <v>2.02</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -13765,733 +13535,698 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DANGEE</t>
+          <t>STUDDS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dangee Dums Limited</t>
+          <t>Studds Accessories Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>2.92</v>
+        <v>393.85</v>
       </c>
       <c r="D32" t="n">
-        <v>2.82</v>
+        <v>417.34</v>
       </c>
       <c r="E32" t="n">
-        <v>3.5</v>
+        <v>-5.6</v>
       </c>
       <c r="F32" t="n">
-        <v>64.45</v>
+        <v>61.75</v>
       </c>
       <c r="G32" t="n">
-        <v>2.02</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STUDDS</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Studds Accessories Limited</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>393.85</v>
+        <v>151.41</v>
       </c>
       <c r="D33" t="n">
-        <v>417.34</v>
+        <v>176.53</v>
       </c>
       <c r="E33" t="n">
-        <v>-5.6</v>
+        <v>-14.2</v>
       </c>
       <c r="F33" t="n">
-        <v>61.75</v>
+        <v>64.08</v>
       </c>
       <c r="G33" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>151.41</v>
+        <v>468.65</v>
       </c>
       <c r="D34" t="n">
-        <v>176.53</v>
+        <v>349.57</v>
       </c>
       <c r="E34" t="n">
-        <v>-14.2</v>
+        <v>34.1</v>
       </c>
       <c r="F34" t="n">
-        <v>64.08</v>
+        <v>70.55</v>
       </c>
       <c r="G34" t="n">
-        <v>1.4</v>
+        <v>31.6</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>468.65</v>
+        <v>156.18</v>
       </c>
       <c r="D35" t="n">
-        <v>349.57</v>
+        <v>159.62</v>
       </c>
       <c r="E35" t="n">
-        <v>34.1</v>
+        <v>-2.2</v>
       </c>
       <c r="F35" t="n">
-        <v>70.55</v>
+        <v>65.64</v>
       </c>
       <c r="G35" t="n">
-        <v>31.6</v>
+        <v>3.99</v>
       </c>
       <c r="H35" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>17-09-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>156.18</v>
+        <v>39.42</v>
       </c>
       <c r="D36" t="n">
-        <v>159.62</v>
+        <v>42.6</v>
       </c>
       <c r="E36" t="n">
-        <v>-2.2</v>
+        <v>-7.5</v>
       </c>
       <c r="F36" t="n">
-        <v>65.64</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99</v>
+        <v>1.4</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>17-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>Maharashtra Seamless Limited</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39.42</v>
+        <v>737.65</v>
       </c>
       <c r="D37" t="n">
-        <v>42.6</v>
+        <v>618.78</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.5</v>
+        <v>19.2</v>
       </c>
       <c r="F37" t="n">
-        <v>71.79000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="G37" t="n">
-        <v>1.4</v>
+        <v>102.7</v>
       </c>
       <c r="H37" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>30-06-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Maharashtra Seamless Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>737.65</v>
+        <v>189.62</v>
       </c>
       <c r="D38" t="n">
-        <v>618.78</v>
+        <v>191.87</v>
       </c>
       <c r="E38" t="n">
-        <v>19.2</v>
+        <v>-1.2</v>
       </c>
       <c r="F38" t="n">
-        <v>67.86</v>
+        <v>70.02</v>
       </c>
       <c r="G38" t="n">
-        <v>102.7</v>
+        <v>1.34</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>189.62</v>
+        <v>196.38</v>
       </c>
       <c r="D39" t="n">
-        <v>191.87</v>
+        <v>195.05</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2</v>
+        <v>0.7</v>
       </c>
       <c r="F39" t="n">
-        <v>70.02</v>
+        <v>60.6</v>
       </c>
       <c r="G39" t="n">
-        <v>1.34</v>
+        <v>0.45</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>25-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>SOTL</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Savita Oil Technologies Limited</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>196.38</v>
+        <v>718.8</v>
       </c>
       <c r="D40" t="n">
-        <v>195.05</v>
+        <v>726.25</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7</v>
+        <v>-1</v>
       </c>
       <c r="F40" t="n">
-        <v>60.6</v>
+        <v>71.92</v>
       </c>
       <c r="G40" t="n">
-        <v>0.45</v>
+        <v>3.76</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>25-09-2026</t>
+          <t>24-09-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SOTL</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Savita Oil Technologies Limited</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>718.8</v>
+        <v>182.73</v>
       </c>
       <c r="D41" t="n">
-        <v>726.25</v>
+        <v>170.45</v>
       </c>
       <c r="E41" t="n">
-        <v>-1</v>
+        <v>7.2</v>
       </c>
       <c r="F41" t="n">
-        <v>71.92</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>3.76</v>
+        <v>0.26</v>
       </c>
       <c r="H41" t="n">
         <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>24-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>182.73</v>
+        <v>21.8</v>
       </c>
       <c r="D42" t="n">
-        <v>170.45</v>
+        <v>21.01</v>
       </c>
       <c r="E42" t="n">
-        <v>7.2</v>
+        <v>3.8</v>
       </c>
       <c r="F42" t="n">
-        <v>67.54000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="G42" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>21.8</v>
+        <v>389.15</v>
       </c>
       <c r="D43" t="n">
-        <v>21.01</v>
+        <v>338.1</v>
       </c>
       <c r="E43" t="n">
-        <v>3.8</v>
+        <v>15.1</v>
       </c>
       <c r="F43" t="n">
-        <v>70.87</v>
+        <v>66.73</v>
       </c>
       <c r="G43" t="n">
-        <v>0.5</v>
+        <v>0.34</v>
       </c>
       <c r="H43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>389.15</v>
+        <v>35.05</v>
       </c>
       <c r="D44" t="n">
-        <v>338.1</v>
+        <v>23.55</v>
       </c>
       <c r="E44" t="n">
-        <v>15.1</v>
+        <v>48.8</v>
       </c>
       <c r="F44" t="n">
-        <v>66.73</v>
+        <v>68.34</v>
       </c>
       <c r="G44" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>35.05</v>
+        <v>666.2</v>
       </c>
       <c r="D45" t="n">
-        <v>23.55</v>
+        <v>593.62</v>
       </c>
       <c r="E45" t="n">
-        <v>48.8</v>
+        <v>12.2</v>
       </c>
       <c r="F45" t="n">
-        <v>68.34</v>
+        <v>74.02</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H45" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>SENCO GOLD LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>666.2</v>
+        <v>320.95</v>
       </c>
       <c r="D46" t="n">
-        <v>593.62</v>
+        <v>335.41</v>
       </c>
       <c r="E46" t="n">
-        <v>12.2</v>
+        <v>-4.3</v>
       </c>
       <c r="F46" t="n">
-        <v>74.02</v>
+        <v>68.48</v>
       </c>
       <c r="G46" t="n">
-        <v>0.25</v>
+        <v>0.41</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>MASFIN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SENCO GOLD LIMITED</t>
+          <t>MAS Financial Services Limited</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>320.95</v>
+        <v>282.7</v>
       </c>
       <c r="D47" t="n">
-        <v>335.41</v>
+        <v>278.98</v>
       </c>
       <c r="E47" t="n">
-        <v>-4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F47" t="n">
-        <v>68.48</v>
+        <v>73.72</v>
       </c>
       <c r="G47" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="H47" t="n">
         <v>2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MASFIN</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MAS Financial Services Limited</t>
+          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>282.7</v>
+        <v>182.18</v>
       </c>
       <c r="D48" t="n">
-        <v>278.98</v>
+        <v>207.63</v>
       </c>
       <c r="E48" t="n">
-        <v>1.3</v>
+        <v>-12.3</v>
       </c>
       <c r="F48" t="n">
-        <v>73.72</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="G48" t="n">
-        <v>0.28</v>
+        <v>4.7</v>
       </c>
       <c r="H48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SANDUR MANGANESE &amp; IRON ORES LIMITED</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>182.18</v>
+        <v>112.09</v>
       </c>
       <c r="D49" t="n">
-        <v>207.63</v>
+        <v>111.01</v>
       </c>
       <c r="E49" t="n">
-        <v>-12.3</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>74.26000000000001</v>
+        <v>73.48</v>
       </c>
       <c r="G49" t="n">
-        <v>4.7</v>
+        <v>0.45</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>NPST</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>112.09</v>
+        <v>1764.8</v>
       </c>
       <c r="D50" t="n">
-        <v>111.01</v>
+        <v>789.9400000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>123.4</v>
       </c>
       <c r="F50" t="n">
-        <v>73.48</v>
+        <v>67.55</v>
       </c>
       <c r="G50" t="n">
-        <v>0.45</v>
+        <v>12.76</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NPST</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NETWORK PEOPLE SERVICES TECHNOLOGIES LIMITED</t>
+          <t>JINDAL STEEL LIMITED</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1764.8</v>
+        <v>1134.9</v>
       </c>
       <c r="D51" t="n">
-        <v>789.9400000000001</v>
+        <v>1157.18</v>
       </c>
       <c r="E51" t="n">
-        <v>123.4</v>
+        <v>-1.9</v>
       </c>
       <c r="F51" t="n">
-        <v>67.55</v>
+        <v>61.21</v>
       </c>
       <c r="G51" t="n">
-        <v>12.76</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I51" t="inlineStr">
-        <is>
-          <t>25-06-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>JINDAL STEEL LIMITED</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>1134.9</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1157.18</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="F52" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="G52" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="inlineStr">
         <is>
           <t>03-09-2026</t>
         </is>
@@ -14540,7 +14275,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -14570,7 +14305,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -14580,7 +14315,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8">

--- a/output/2026-10-01/enriched_analysis.xlsx
+++ b/output/2026-10-01/enriched_analysis.xlsx
@@ -929,13 +929,13 @@
         </is>
       </c>
       <c r="V2" t="n">
-        <v>2.664</v>
+        <v>2.702</v>
       </c>
       <c r="W2" t="n">
-        <v>2928</v>
+        <v>2886</v>
       </c>
       <c r="X2" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="Y2" t="n">
         <v>75</v>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="V3" t="n">
-        <v>0.533</v>
+        <v>0.537</v>
       </c>
       <c r="W3" t="n">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="X3" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Y3" t="n">
         <v>47</v>
@@ -1396,10 +1396,10 @@
         <v>0.049</v>
       </c>
       <c r="W4" t="n">
-        <v>2729</v>
+        <v>2721</v>
       </c>
       <c r="X4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="Y4" t="n">
         <v>36</v>
@@ -1625,13 +1625,13 @@
         </is>
       </c>
       <c r="V5" t="n">
-        <v>0.952</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="X5" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="Y5" t="n">
         <v>22</v>
@@ -1857,13 +1857,13 @@
         </is>
       </c>
       <c r="V6" t="n">
-        <v>0.316</v>
+        <v>0.321</v>
       </c>
       <c r="W6" t="n">
-        <v>968</v>
+        <v>955</v>
       </c>
       <c r="X6" t="n">
-        <v>9.52</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Y6" t="n">
         <v>7</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="V7" t="n">
-        <v>0.993</v>
+        <v>0.979</v>
       </c>
       <c r="W7" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="X7" t="n">
-        <v>8.6</v>
+        <v>8.73</v>
       </c>
       <c r="Y7" t="n">
         <v>17</v>
@@ -2321,13 +2321,13 @@
         </is>
       </c>
       <c r="V8" t="n">
-        <v>2.212</v>
+        <v>2.262</v>
       </c>
       <c r="W8" t="n">
-        <v>2653</v>
+        <v>2595</v>
       </c>
       <c r="X8" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="Y8" t="n">
         <v>6</v>
@@ -2553,13 +2553,13 @@
         </is>
       </c>
       <c r="V9" t="n">
-        <v>0.472</v>
+        <v>0.48</v>
       </c>
       <c r="W9" t="n">
-        <v>2753</v>
+        <v>2704</v>
       </c>
       <c r="X9" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="Y9" t="n">
         <v>8</v>
@@ -2713,12 +2713,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2730,40 +2730,40 @@
         </is>
       </c>
       <c r="E10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F10" t="n">
         <v>5</v>
       </c>
-      <c r="F10" t="n">
-        <v>22</v>
-      </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>68.59999999999999</v>
+        <v>1043.35</v>
       </c>
       <c r="J10" t="n">
-        <v>64.48999999999999</v>
+        <v>799.34</v>
       </c>
       <c r="K10" t="n">
-        <v>6.4</v>
+        <v>30.5</v>
       </c>
       <c r="L10" t="n">
-        <v>64.29000000000001</v>
+        <v>61.71</v>
       </c>
       <c r="M10" t="n">
-        <v>0.57</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5656038</v>
+        <v>32023110</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>5656038</v>
+        <v>32023110</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -2777,62 +2777,62 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>8</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>28-09-2026</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>1.013</v>
+      </c>
+      <c r="W10" t="n">
+        <v>316</v>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
         <v>9</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>18-09-2026</t>
-        </is>
-      </c>
-      <c r="V10" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="W10" t="n">
-        <v>843</v>
-      </c>
-      <c r="X10" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>19</v>
-      </c>
       <c r="Z10" t="n">
-        <v>12.31</v>
+        <v>11.91</v>
       </c>
       <c r="AA10" t="n">
-        <v>41</v>
+        <v>-184</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8</v>
+        <v>31.98</v>
       </c>
       <c r="AC10" t="n">
-        <v>22.2</v>
+        <v>-0.26</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AE10" t="b">
         <v>1</v>
       </c>
       <c r="AF10" t="n">
-        <v>12.14</v>
+        <v>57.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="AH10" t="inlineStr"/>
+        <v>816.35</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>787.17</v>
+      </c>
       <c r="AI10" t="n">
-        <v>35.4</v>
+        <v>28.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>64.49302166476625</v>
+        <v>799.3387748989066</v>
       </c>
       <c r="AK10" t="n">
-        <v>6.4</v>
+        <v>30.5</v>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -2852,47 +2852,47 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AR10" t="n">
         <v>45</v>
       </c>
       <c r="AS10" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
         <v>4</v>
       </c>
       <c r="AV10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>3257615</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1628129</v>
+        <v>10731521</v>
       </c>
       <c r="BA10" t="n">
-        <v>2601121</v>
+        <v>15906207</v>
       </c>
       <c r="BB10" t="n">
-        <v>5656038</v>
+        <v>32023110</v>
       </c>
       <c r="BC10" t="n">
-        <v>5656038</v>
+        <v>32023110</v>
       </c>
       <c r="BD10" t="n">
         <v>0</v>
@@ -2925,34 +2925,34 @@
         <v>0</v>
       </c>
       <c r="BN10" t="n">
-        <v>0</v>
+        <v>3257615</v>
       </c>
       <c r="BO10" t="n">
-        <v>2601121</v>
+        <v>15906207</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BQ10" t="n">
         <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>0</v>
+        <v>0.2048</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2960,40 +2960,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>5062</v>
+        <v>140.49</v>
       </c>
       <c r="J11" t="n">
-        <v>5198.76</v>
+        <v>171.54</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.6</v>
+        <v>-18.1</v>
       </c>
       <c r="L11" t="n">
-        <v>67.16</v>
+        <v>74.59</v>
       </c>
       <c r="M11" t="n">
-        <v>7.21</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>72054758</v>
+        <v>11081344</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>72054758</v>
+        <v>11081344</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -3007,124 +3007,124 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V11" t="n">
-        <v>0.046</v>
+        <v>0.063</v>
       </c>
       <c r="W11" t="n">
-        <v>15734</v>
+        <v>1761</v>
       </c>
       <c r="X11" t="n">
-        <v>40.1</v>
+        <v>40.4</v>
       </c>
       <c r="Y11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA11" t="n">
         <v>83</v>
       </c>
-      <c r="Z11" t="n">
-        <v>145</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>264</v>
-      </c>
       <c r="AB11" t="n">
-        <v>27.38</v>
+        <v>0.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.5</v>
+        <v>30.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.64</v>
+        <v>0.2</v>
       </c>
       <c r="AE11" t="b">
         <v>1</v>
       </c>
       <c r="AF11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>178.38</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>487.24</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>171.5378328173375</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>-18.1</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>30-09-2026</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>36</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>37</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW11" t="n">
         <v>5</v>
       </c>
-      <c r="AG11" t="n">
-        <v>5436.1</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>4485.08</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>5198.755988455989</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>Aging</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Mature Accumulation</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="AQ11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>58</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>31</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>6</v>
-      </c>
       <c r="AX11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>83720</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>83720</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>6160489</v>
       </c>
       <c r="BB11" t="n">
-        <v>72054758</v>
+        <v>11081344</v>
       </c>
       <c r="BC11" t="n">
-        <v>72054758</v>
+        <v>11081344</v>
       </c>
       <c r="BD11" t="n">
         <v>0</v>
@@ -3157,34 +3157,34 @@
         <v>0</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>83720</v>
       </c>
       <c r="BO11" t="n">
-        <v>0</v>
+        <v>6160489</v>
       </c>
       <c r="BP11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ11" t="n">
         <v>0</v>
       </c>
       <c r="BR11" t="n">
-        <v>0</v>
+        <v>0.0136</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3192,40 +3192,40 @@
         </is>
       </c>
       <c r="E12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>22</v>
+      </c>
+      <c r="G12" t="n">
         <v>17</v>
       </c>
-      <c r="F12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G12" t="n">
-        <v>25</v>
-      </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1043.35</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>799.34</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>30.5</v>
+        <v>6.4</v>
       </c>
       <c r="L12" t="n">
-        <v>61.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>0.57</v>
       </c>
       <c r="N12" t="n">
-        <v>32023110</v>
+        <v>5656038</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>32023110</v>
+        <v>5656038</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -3239,62 +3239,62 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="V12" t="n">
-        <v>0.991</v>
+        <v>0.065</v>
       </c>
       <c r="W12" t="n">
-        <v>323</v>
-      </c>
-      <c r="X12" t="inlineStr"/>
+        <v>871</v>
+      </c>
+      <c r="X12" t="n">
+        <v>22</v>
+      </c>
       <c r="Y12" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.91</v>
+        <v>12.31</v>
       </c>
       <c r="AA12" t="n">
-        <v>-184</v>
+        <v>41</v>
       </c>
       <c r="AB12" t="n">
-        <v>31.98</v>
+        <v>0.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.26</v>
+        <v>22.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AE12" t="b">
         <v>1</v>
       </c>
       <c r="AF12" t="n">
-        <v>57.93</v>
+        <v>12.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>816.35</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>787.17</v>
-      </c>
+        <v>66.02</v>
+      </c>
+      <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="n">
-        <v>28.8</v>
+        <v>35.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>799.3387748989066</v>
+        <v>64.49302166476625</v>
       </c>
       <c r="AK12" t="n">
-        <v>30.5</v>
+        <v>6.4</v>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -3314,47 +3314,47 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="AR12" t="n">
         <v>45</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AT12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
         <v>4</v>
       </c>
       <c r="AV12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>3257615</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10731521</v>
+        <v>1628129</v>
       </c>
       <c r="BA12" t="n">
-        <v>15906207</v>
+        <v>2601121</v>
       </c>
       <c r="BB12" t="n">
-        <v>32023110</v>
+        <v>5656038</v>
       </c>
       <c r="BC12" t="n">
-        <v>32023110</v>
+        <v>5656038</v>
       </c>
       <c r="BD12" t="n">
         <v>0</v>
@@ -3387,34 +3387,34 @@
         <v>0</v>
       </c>
       <c r="BN12" t="n">
-        <v>3257615</v>
+        <v>0</v>
       </c>
       <c r="BO12" t="n">
-        <v>15906207</v>
+        <v>2601121</v>
       </c>
       <c r="BP12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BQ12" t="n">
         <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.2048</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -3422,40 +3422,40 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>72.29000000000001</v>
+        <v>5062</v>
       </c>
       <c r="J13" t="n">
-        <v>68.68000000000001</v>
+        <v>5198.76</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>-2.6</v>
       </c>
       <c r="L13" t="n">
-        <v>71.22</v>
+        <v>67.16</v>
       </c>
       <c r="M13" t="n">
-        <v>0.86</v>
+        <v>7.21</v>
       </c>
       <c r="N13" t="n">
-        <v>8585000</v>
+        <v>72054758</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>8585000</v>
+        <v>72054758</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -3469,118 +3469,124 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="V13" t="n">
-        <v>0.125</v>
+        <v>0.047</v>
       </c>
       <c r="W13" t="n">
-        <v>686</v>
+        <v>15396</v>
       </c>
       <c r="X13" t="n">
-        <v>29.9</v>
+        <v>39.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.44</v>
+        <v>145</v>
       </c>
       <c r="AA13" t="n">
-        <v>39</v>
+        <v>264</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.55</v>
+        <v>27.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.9</v>
+        <v>25.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.25</v>
+        <v>0.64</v>
       </c>
       <c r="AE13" t="b">
         <v>1</v>
       </c>
       <c r="AF13" t="n">
-        <v>19.61</v>
-      </c>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5436.1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4485.08</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>47.5</v>
+      </c>
       <c r="AJ13" t="n">
-        <v>68.68000000000001</v>
+        <v>5198.755988455989</v>
       </c>
       <c r="AK13" t="n">
-        <v>5.3</v>
+        <v>-2.6</v>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AR13" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="AS13" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>8585000</v>
+        <v>72054758</v>
       </c>
       <c r="BC13" t="n">
-        <v>8585000</v>
+        <v>72054758</v>
       </c>
       <c r="BD13" t="n">
         <v>0</v>
@@ -3613,34 +3619,34 @@
         <v>0</v>
       </c>
       <c r="BN13" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BO13" t="n">
-        <v>8585000</v>
+        <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ13" t="n">
         <v>0</v>
       </c>
       <c r="BR13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -3648,40 +3654,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F14" t="n">
         <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>406.45</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>217.8</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>86.59999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
-        <v>71.75</v>
+        <v>71.22</v>
       </c>
       <c r="M14" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="N14" t="n">
-        <v>8227124</v>
+        <v>8585000</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>8227124</v>
+        <v>8585000</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -3695,124 +3701,118 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="V14" t="n">
-        <v>0.046</v>
+        <v>0.124</v>
       </c>
       <c r="W14" t="n">
-        <v>1774</v>
+        <v>691</v>
       </c>
       <c r="X14" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>39</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AC14" t="n">
         <v>23.9</v>
       </c>
-      <c r="Y14" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>54</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>11</v>
-      </c>
       <c r="AD14" t="n">
-        <v>0.01</v>
+        <v>0.25</v>
       </c>
       <c r="AE14" t="b">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>263.59</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>196.11</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>203.2</v>
-      </c>
+        <v>19.61</v>
+      </c>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="n">
-        <v>217.7985916238683</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="AK14" t="n">
-        <v>86.59999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="AS14" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AX14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BB14" t="n">
-        <v>8227124</v>
+        <v>8585000</v>
       </c>
       <c r="BC14" t="n">
-        <v>8227124</v>
+        <v>8585000</v>
       </c>
       <c r="BD14" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>8585000</v>
       </c>
       <c r="BP14" t="n">
         <v>1</v>
@@ -3857,22 +3857,22 @@
         <v>0</v>
       </c>
       <c r="BR14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3880,10 +3880,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G15" t="n">
         <v>25</v>
@@ -3892,28 +3892,28 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>100.36</v>
+        <v>406.45</v>
       </c>
       <c r="J15" t="n">
-        <v>75.68000000000001</v>
+        <v>217.8</v>
       </c>
       <c r="K15" t="n">
-        <v>32.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>74.84999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.14</v>
+        <v>0.82</v>
       </c>
       <c r="N15" t="n">
-        <v>31393588</v>
+        <v>8227124</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>31393588</v>
+        <v>8227124</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -3927,69 +3927,69 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="V15" t="n">
-        <v>0.12</v>
+        <v>0.049</v>
       </c>
       <c r="W15" t="n">
-        <v>2621</v>
+        <v>1691</v>
       </c>
       <c r="X15" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>-3</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="AA15" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.29</v>
+        <v>8.23</v>
       </c>
       <c r="AC15" t="n">
-        <v>15.8</v>
+        <v>11</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.69</v>
+        <v>0.01</v>
       </c>
       <c r="AE15" t="b">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>70.39</v>
+        <v>263.59</v>
       </c>
       <c r="AH15" t="n">
-        <v>48.47</v>
+        <v>196.11</v>
       </c>
       <c r="AI15" t="n">
-        <v>223.4</v>
+        <v>203.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75.6844038997483</v>
+        <v>217.7985916238683</v>
       </c>
       <c r="AK15" t="n">
-        <v>32.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -3999,22 +3999,22 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
@@ -4023,13 +4023,13 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AX15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
         <v>0</v>
@@ -4038,13 +4038,13 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>31393588</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>31393588</v>
+        <v>8227124</v>
       </c>
       <c r="BC15" t="n">
-        <v>31393588</v>
+        <v>8227124</v>
       </c>
       <c r="BD15" t="n">
         <v>0</v>
@@ -4080,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>31393588</v>
+        <v>0</v>
       </c>
       <c r="BP15" t="n">
         <v>1</v>
@@ -4095,16 +4095,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4112,40 +4112,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>142.41</v>
+        <v>100.36</v>
       </c>
       <c r="J16" t="n">
-        <v>143.72</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9</v>
+        <v>32.6</v>
       </c>
       <c r="L16" t="n">
-        <v>63.69</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>19.68</v>
+        <v>3.14</v>
       </c>
       <c r="N16" t="n">
-        <v>196783125</v>
+        <v>31393588</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>196783125</v>
+        <v>31393588</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -4159,54 +4159,60 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="V16" t="n">
-        <v>2.835</v>
+        <v>0.128</v>
       </c>
       <c r="W16" t="n">
-        <v>694</v>
+        <v>2462</v>
       </c>
       <c r="X16" t="n">
-        <v>26.1</v>
+        <v>21.6</v>
       </c>
       <c r="Y16" t="n">
-        <v>30</v>
+        <v>-3</v>
       </c>
       <c r="Z16" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="AA16" t="n">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.88</v>
+        <v>1.29</v>
       </c>
       <c r="AC16" t="n">
-        <v>14.1</v>
+        <v>15.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.32</v>
+        <v>1.69</v>
       </c>
       <c r="AE16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>70.39</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>223.4</v>
+      </c>
       <c r="AJ16" t="n">
-        <v>143.7164139971926</v>
+        <v>75.6844038997483</v>
       </c>
       <c r="AK16" t="n">
-        <v>-0.9</v>
+        <v>32.6</v>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
@@ -4220,57 +4226,57 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>196783125</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>196783125</v>
+        <v>31393588</v>
       </c>
       <c r="BB16" t="n">
-        <v>196783125</v>
+        <v>31393588</v>
       </c>
       <c r="BC16" t="n">
-        <v>196783125</v>
+        <v>31393588</v>
       </c>
       <c r="BD16" t="n">
         <v>0</v>
@@ -4306,7 +4312,7 @@
         <v>0</v>
       </c>
       <c r="BO16" t="n">
-        <v>196783125</v>
+        <v>31393588</v>
       </c>
       <c r="BP16" t="n">
         <v>1</v>
@@ -4330,7 +4336,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4338,7 +4344,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F17" t="n">
         <v>8</v>
@@ -4393,13 +4399,13 @@
         </is>
       </c>
       <c r="V17" t="n">
-        <v>0.495</v>
+        <v>0.503</v>
       </c>
       <c r="W17" t="n">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="X17" t="n">
-        <v>37.4</v>
+        <v>36.8</v>
       </c>
       <c r="Y17" t="n">
         <v>21</v>
@@ -4553,57 +4559,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="F18" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>140.49</v>
+        <v>142.41</v>
       </c>
       <c r="J18" t="n">
-        <v>171.84</v>
+        <v>143.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-18.2</v>
+        <v>-0.9</v>
       </c>
       <c r="L18" t="n">
-        <v>74.59</v>
+        <v>63.69</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>19.68</v>
       </c>
       <c r="N18" t="n">
-        <v>10997624</v>
+        <v>196783125</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>10997624</v>
+        <v>196783125</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -4621,56 +4627,50 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="V18" t="n">
-        <v>0.062</v>
+        <v>2.831</v>
       </c>
       <c r="W18" t="n">
-        <v>1782</v>
+        <v>695</v>
       </c>
       <c r="X18" t="n">
-        <v>40.9</v>
+        <v>26.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="Z18" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="AA18" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.8</v>
+        <v>7.88</v>
       </c>
       <c r="AC18" t="n">
-        <v>30.3</v>
+        <v>14.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>178.38</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>487.24</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>29.5</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
       <c r="AJ18" t="n">
-        <v>171.837875</v>
+        <v>143.7164139971926</v>
       </c>
       <c r="AK18" t="n">
-        <v>-18.2</v>
+        <v>-0.9</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -4689,31 +4689,31 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="AR18" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
         <v>4</v>
@@ -4725,16 +4725,16 @@
         <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>196783125</v>
       </c>
       <c r="BA18" t="n">
-        <v>6076769</v>
+        <v>196783125</v>
       </c>
       <c r="BB18" t="n">
-        <v>10997624</v>
+        <v>196783125</v>
       </c>
       <c r="BC18" t="n">
-        <v>10997624</v>
+        <v>196783125</v>
       </c>
       <c r="BD18" t="n">
         <v>0</v>
@@ -4770,7 +4770,7 @@
         <v>0</v>
       </c>
       <c r="BO18" t="n">
-        <v>6076769</v>
+        <v>196783125</v>
       </c>
       <c r="BP18" t="n">
         <v>1</v>
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="V19" t="n">
-        <v>0.321</v>
+        <v>0.316</v>
       </c>
       <c r="W19" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="X19" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="Y19" t="n">
         <v>12</v>
@@ -5089,13 +5089,13 @@
         </is>
       </c>
       <c r="V20" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="W20" t="n">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="X20" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="Y20" t="n">
         <v>21</v>
@@ -5321,13 +5321,13 @@
         </is>
       </c>
       <c r="V21" t="n">
-        <v>0.649</v>
+        <v>0.651</v>
       </c>
       <c r="W21" t="n">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="X21" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="Y21" t="n">
         <v>19</v>
@@ -5553,13 +5553,13 @@
         </is>
       </c>
       <c r="V22" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>670</v>
+        <v>651</v>
       </c>
       <c r="X22" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="Y22" t="n">
         <v>-5</v>
@@ -5788,10 +5788,10 @@
         <v>0.008999999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>53106</v>
+        <v>52727</v>
       </c>
       <c r="X23" t="n">
-        <v>45</v>
+        <v>44.6</v>
       </c>
       <c r="Y23" t="n">
         <v>5</v>
@@ -6017,13 +6017,13 @@
         </is>
       </c>
       <c r="V24" t="n">
-        <v>0.183</v>
+        <v>0.184</v>
       </c>
       <c r="W24" t="n">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="X24" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="Y24" t="n">
         <v>3</v>
@@ -6041,7 +6041,7 @@
         <v>11.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="V25" t="n">
-        <v>0.927</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="X25" t="n">
-        <v>6.27</v>
+        <v>6.16</v>
       </c>
       <c r="Y25" t="n">
         <v>31</v>
@@ -6477,13 +6477,13 @@
         </is>
       </c>
       <c r="V26" t="n">
-        <v>0.643</v>
+        <v>0.633</v>
       </c>
       <c r="W26" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="X26" t="n">
-        <v>1178</v>
+        <v>1197</v>
       </c>
       <c r="Y26" t="n">
         <v>-61</v>
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="V27" t="n">
-        <v>1.876</v>
+        <v>1.926</v>
       </c>
       <c r="W27" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
@@ -6935,13 +6935,13 @@
         </is>
       </c>
       <c r="V28" t="n">
-        <v>0.274</v>
+        <v>0.276</v>
       </c>
       <c r="W28" t="n">
-        <v>950</v>
+        <v>942</v>
       </c>
       <c r="X28" t="n">
-        <v>25.9</v>
+        <v>25.6</v>
       </c>
       <c r="Y28" t="n">
         <v>9</v>
@@ -7167,13 +7167,13 @@
         </is>
       </c>
       <c r="V29" t="n">
-        <v>0.495</v>
+        <v>0.5</v>
       </c>
       <c r="W29" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="X29" t="n">
-        <v>37.6</v>
+        <v>37.2</v>
       </c>
       <c r="Y29" t="n">
         <v>-44</v>
@@ -7399,13 +7399,13 @@
         </is>
       </c>
       <c r="V30" t="n">
-        <v>0.199</v>
+        <v>0.204</v>
       </c>
       <c r="W30" t="n">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="X30" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="Y30" t="n">
         <v>16</v>
@@ -7860,10 +7860,10 @@
         <v>0.045</v>
       </c>
       <c r="W32" t="n">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="X32" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Y32" t="n">
         <v>10</v>
@@ -8092,7 +8092,7 @@
         <v>0.229</v>
       </c>
       <c r="W33" t="n">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="X33" t="n">
         <v>13.5</v>
@@ -8321,13 +8321,13 @@
         </is>
       </c>
       <c r="V34" t="n">
-        <v>0.786</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>4019</v>
+        <v>3903</v>
       </c>
       <c r="X34" t="n">
-        <v>28.1</v>
+        <v>27.3</v>
       </c>
       <c r="Y34" t="n">
         <v>2</v>
@@ -8553,13 +8553,13 @@
         </is>
       </c>
       <c r="V35" t="n">
-        <v>0.23</v>
+        <v>0.227</v>
       </c>
       <c r="W35" t="n">
-        <v>1734</v>
+        <v>1758</v>
       </c>
       <c r="X35" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="Y35" t="n">
         <v>-3</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="V36" t="n">
-        <v>0.359</v>
+        <v>0.363</v>
       </c>
       <c r="W36" t="n">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="X36" t="n">
-        <v>96.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="Y36" t="n">
         <v>246</v>
@@ -9017,13 +9017,13 @@
         </is>
       </c>
       <c r="V37" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="W37" t="n">
-        <v>9884</v>
+        <v>9515</v>
       </c>
       <c r="X37" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="Y37" t="n">
         <v>-12</v>
@@ -9249,13 +9249,13 @@
         </is>
       </c>
       <c r="V38" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
       <c r="W38" t="n">
-        <v>3328</v>
+        <v>3310</v>
       </c>
       <c r="X38" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="Y38" t="n">
         <v>-4</v>
@@ -9484,7 +9484,7 @@
         <v>0.011</v>
       </c>
       <c r="W39" t="n">
-        <v>4163</v>
+        <v>4127</v>
       </c>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="n">
@@ -9714,10 +9714,10 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>4928</v>
+        <v>4932</v>
       </c>
       <c r="X40" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="Y40" t="n">
         <v>26</v>
@@ -9943,13 +9943,13 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>0.104</v>
+        <v>0.106</v>
       </c>
       <c r="W41" t="n">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="X41" t="n">
-        <v>26.3</v>
+        <v>25.8</v>
       </c>
       <c r="Y41" t="n">
         <v>24</v>
@@ -10175,13 +10175,13 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>0.12</v>
+        <v>0.114</v>
       </c>
       <c r="W42" t="n">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="X42" t="n">
-        <v>6.7</v>
+        <v>7.09</v>
       </c>
       <c r="Y42" t="n">
         <v>118</v>
@@ -10331,16 +10331,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -10348,40 +10348,40 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F43" t="n">
-        <v>15</v>
+        <v>-5</v>
       </c>
       <c r="G43" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>389.15</v>
+        <v>666.2</v>
       </c>
       <c r="J43" t="n">
-        <v>338.1</v>
+        <v>622.4400000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>15.1</v>
+        <v>7</v>
       </c>
       <c r="L43" t="n">
-        <v>66.73</v>
+        <v>74.02</v>
       </c>
       <c r="M43" t="n">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="N43" t="n">
-        <v>3381000</v>
+        <v>4930931</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>3381000</v>
+        <v>4930931</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -10395,124 +10395,122 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="V43" t="n">
-        <v>0.074</v>
+        <v>0.05</v>
       </c>
       <c r="W43" t="n">
-        <v>459</v>
-      </c>
-      <c r="X43" t="n">
-        <v>13.6</v>
-      </c>
+        <v>983</v>
+      </c>
+      <c r="X43" t="inlineStr"/>
       <c r="Y43" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="Z43" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="AA43" t="n">
-        <v>33</v>
+        <v>-152</v>
       </c>
       <c r="AB43" t="n">
-        <v>14.36</v>
+        <v>-6.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>9.94</v>
+        <v>9.24</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.23</v>
+        <v>2.23</v>
       </c>
       <c r="AE43" t="b">
         <v>1</v>
       </c>
       <c r="AF43" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AG43" t="n">
-        <v>366.73</v>
+        <v>598.4</v>
       </c>
       <c r="AH43" t="n">
-        <v>272.07</v>
+        <v>549.58</v>
       </c>
       <c r="AI43" t="n">
-        <v>99.5</v>
+        <v>36.6</v>
       </c>
       <c r="AJ43" t="n">
-        <v>338.1</v>
+        <v>622.4351173945973</v>
       </c>
       <c r="AK43" t="n">
-        <v>15.1</v>
+        <v>7</v>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AR43" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="AS43" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AY43" t="n">
-        <v>0</v>
+        <v>2472736</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>2472736</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>3760931</v>
       </c>
       <c r="BB43" t="n">
-        <v>3381000</v>
+        <v>4930931</v>
       </c>
       <c r="BC43" t="n">
-        <v>3381000</v>
+        <v>4930931</v>
       </c>
       <c r="BD43" t="n">
         <v>0</v>
@@ -10545,34 +10543,34 @@
         <v>0</v>
       </c>
       <c r="BN43" t="n">
-        <v>0</v>
+        <v>2472736</v>
       </c>
       <c r="BO43" t="n">
-        <v>0</v>
+        <v>3760931</v>
       </c>
       <c r="BP43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BQ43" t="n">
         <v>0</v>
       </c>
       <c r="BR43" t="n">
-        <v>0</v>
+        <v>0.6575</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -10580,40 +10578,40 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="G44" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>35.05</v>
+        <v>389.15</v>
       </c>
       <c r="J44" t="n">
-        <v>23.55</v>
+        <v>338.1</v>
       </c>
       <c r="K44" t="n">
-        <v>48.8</v>
+        <v>15.1</v>
       </c>
       <c r="L44" t="n">
-        <v>68.34</v>
+        <v>66.73</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="N44" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -10627,124 +10625,124 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="V44" t="n">
-        <v>0.113</v>
+        <v>0.075</v>
       </c>
       <c r="W44" t="n">
-        <v>179</v>
+        <v>450</v>
       </c>
       <c r="X44" t="n">
-        <v>41.4</v>
+        <v>13.3</v>
       </c>
       <c r="Y44" t="n">
-        <v>19</v>
+        <v>-8</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.17</v>
+        <v>24</v>
       </c>
       <c r="AA44" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.49</v>
+        <v>14.36</v>
       </c>
       <c r="AC44" t="n">
-        <v>8.76</v>
+        <v>9.94</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF44" t="n">
-        <v>14.87</v>
+        <v>18</v>
       </c>
       <c r="AG44" t="n">
-        <v>23.74</v>
+        <v>366.73</v>
       </c>
       <c r="AH44" t="n">
-        <v>22.79</v>
+        <v>272.07</v>
       </c>
       <c r="AI44" t="n">
-        <v>92.8</v>
+        <v>99.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>23.5472893358377</v>
+        <v>338.1</v>
       </c>
       <c r="AK44" t="n">
-        <v>48.8</v>
+        <v>15.1</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AQ44" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="AS44" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
       <c r="AU44" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AX44" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AY44" t="n">
         <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1188529</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>1457700</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="BC44" t="n">
-        <v>2018403</v>
+        <v>3381000</v>
       </c>
       <c r="BD44" t="n">
         <v>0</v>
@@ -10780,10 +10778,10 @@
         <v>0</v>
       </c>
       <c r="BO44" t="n">
-        <v>1457700</v>
+        <v>0</v>
       </c>
       <c r="BP44" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BQ44" t="n">
         <v>0</v>
@@ -10795,16 +10793,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -10812,10 +10810,10 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F45" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="G45" t="n">
         <v>25</v>
@@ -10824,28 +10822,28 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>666.2</v>
+        <v>35.05</v>
       </c>
       <c r="J45" t="n">
-        <v>593.62</v>
+        <v>23.55</v>
       </c>
       <c r="K45" t="n">
-        <v>12.2</v>
+        <v>48.8</v>
       </c>
       <c r="L45" t="n">
-        <v>74.02</v>
+        <v>68.34</v>
       </c>
       <c r="M45" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="N45" t="n">
-        <v>2458195</v>
+        <v>2018403</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2458195</v>
+        <v>2018403</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -10859,58 +10857,60 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="V45" t="n">
-        <v>0.024</v>
+        <v>0.119</v>
       </c>
       <c r="W45" t="n">
-        <v>1035</v>
-      </c>
-      <c r="X45" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="X45" t="n">
+        <v>39.4</v>
+      </c>
       <c r="Y45" t="n">
-        <v>-2</v>
+        <v>19</v>
       </c>
       <c r="Z45" t="n">
-        <v>5</v>
+        <v>3.17</v>
       </c>
       <c r="AA45" t="n">
-        <v>-152</v>
+        <v>7</v>
       </c>
       <c r="AB45" t="n">
-        <v>-6.5</v>
+        <v>0.49</v>
       </c>
       <c r="AC45" t="n">
-        <v>9.24</v>
+        <v>8.76</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.23</v>
+        <v>0.2</v>
       </c>
       <c r="AE45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>6</v>
+        <v>14.87</v>
       </c>
       <c r="AG45" t="n">
-        <v>598.4</v>
+        <v>23.74</v>
       </c>
       <c r="AH45" t="n">
-        <v>549.58</v>
+        <v>22.79</v>
       </c>
       <c r="AI45" t="n">
-        <v>36.6</v>
+        <v>92.8</v>
       </c>
       <c r="AJ45" t="n">
-        <v>593.6235208886742</v>
+        <v>23.5472893358377</v>
       </c>
       <c r="AK45" t="n">
-        <v>12.2</v>
+        <v>48.8</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -10924,57 +10924,57 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
       <c r="AQ45" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AR45" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AS45" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV45" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AW45" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AX45" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="AY45" t="n">
         <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1188529</v>
       </c>
       <c r="BA45" t="n">
-        <v>1288195</v>
+        <v>1457700</v>
       </c>
       <c r="BB45" t="n">
-        <v>2458195</v>
+        <v>2018403</v>
       </c>
       <c r="BC45" t="n">
-        <v>2458195</v>
+        <v>2018403</v>
       </c>
       <c r="BD45" t="n">
         <v>0</v>
@@ -11010,10 +11010,10 @@
         <v>0</v>
       </c>
       <c r="BO45" t="n">
-        <v>1288195</v>
+        <v>1457700</v>
       </c>
       <c r="BP45" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BQ45" t="n">
         <v>0</v>
@@ -11100,10 +11100,10 @@
         <v>0.008</v>
       </c>
       <c r="W46" t="n">
-        <v>5260</v>
+        <v>5212</v>
       </c>
       <c r="X46" t="n">
-        <v>8.890000000000001</v>
+        <v>8.84</v>
       </c>
       <c r="Y46" t="n">
         <v>43</v>
@@ -11329,13 +11329,13 @@
         </is>
       </c>
       <c r="V47" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="W47" t="n">
-        <v>5130</v>
+        <v>4936</v>
       </c>
       <c r="X47" t="n">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="Y47" t="n">
         <v>23</v>
@@ -11560,10 +11560,10 @@
         <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>8856</v>
+        <v>8769</v>
       </c>
       <c r="X48" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="Y48" t="n">
         <v>21</v>
@@ -11789,13 +11789,13 @@
         </is>
       </c>
       <c r="V49" t="n">
-        <v>0.211</v>
+        <v>0.213</v>
       </c>
       <c r="W49" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="X49" t="n">
-        <v>25.3</v>
+        <v>25.1</v>
       </c>
       <c r="Y49" t="n">
         <v>21</v>
@@ -12024,10 +12024,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>3682</v>
+        <v>3690</v>
       </c>
       <c r="X50" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="Y50" t="n">
         <v>42</v>
@@ -12256,10 +12256,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>115770</v>
+        <v>113842</v>
       </c>
       <c r="X51" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="Y51" t="n">
         <v>18</v>
@@ -12765,245 +12765,245 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>68.59999999999999</v>
+        <v>1043.35</v>
       </c>
       <c r="D10" t="n">
-        <v>64.48999999999999</v>
+        <v>799.34</v>
       </c>
       <c r="E10" t="n">
-        <v>6.4</v>
+        <v>30.5</v>
       </c>
       <c r="F10" t="n">
-        <v>64.29000000000001</v>
+        <v>61.71</v>
       </c>
       <c r="G10" t="n">
-        <v>0.57</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18-09-2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>THANGAMAYIL JEWELLERY LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5062</v>
+        <v>140.49</v>
       </c>
       <c r="D11" t="n">
-        <v>5198.76</v>
+        <v>171.54</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6</v>
+        <v>-18.1</v>
       </c>
       <c r="F11" t="n">
-        <v>67.16</v>
+        <v>74.59</v>
       </c>
       <c r="G11" t="n">
-        <v>7.21</v>
+        <v>1.11</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1043.35</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>799.34</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>30.5</v>
+        <v>6.4</v>
       </c>
       <c r="F12" t="n">
-        <v>61.71</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>0.57</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>18-09-2026</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HTEL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hy-Tech Engineers Limited</t>
+          <t>THANGAMAYIL JEWELLERY LIMITED</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>72.29000000000001</v>
+        <v>5062</v>
       </c>
       <c r="D13" t="n">
-        <v>68.68000000000001</v>
+        <v>5198.76</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3</v>
+        <v>-2.6</v>
       </c>
       <c r="F13" t="n">
-        <v>71.22</v>
+        <v>67.16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.86</v>
+        <v>7.21</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>29-09-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>HTEL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>Hy-Tech Engineers Limited</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>406.45</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>217.8</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>86.59999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="F14" t="n">
-        <v>71.75</v>
+        <v>71.22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="H14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>29-09-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100.36</v>
+        <v>406.45</v>
       </c>
       <c r="D15" t="n">
-        <v>75.68000000000001</v>
+        <v>217.8</v>
       </c>
       <c r="E15" t="n">
-        <v>32.6</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>74.84999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G15" t="n">
-        <v>3.14</v>
+        <v>0.82</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VEEGALAND</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Veegaland Developers Limited</t>
+          <t>INDO RAMA SYNTHETICS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>142.41</v>
+        <v>100.36</v>
       </c>
       <c r="D16" t="n">
-        <v>143.72</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9</v>
+        <v>32.6</v>
       </c>
       <c r="F16" t="n">
-        <v>63.69</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>19.68</v>
+        <v>3.14</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
     </row>
@@ -13045,35 +13045,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>VEEGALAND</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>Veegaland Developers Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>140.49</v>
+        <v>142.41</v>
       </c>
       <c r="D18" t="n">
-        <v>171.84</v>
+        <v>143.72</v>
       </c>
       <c r="E18" t="n">
-        <v>-18.2</v>
+        <v>-0.9</v>
       </c>
       <c r="F18" t="n">
-        <v>74.59</v>
+        <v>63.69</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1</v>
+        <v>19.68</v>
       </c>
       <c r="H18" t="n">
         <v>4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>22-09-2026</t>
         </is>
       </c>
     </row>
@@ -13920,105 +13920,105 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>SGIL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>389.15</v>
+        <v>666.2</v>
       </c>
       <c r="D43" t="n">
-        <v>338.1</v>
+        <v>622.4400000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>15.1</v>
+        <v>7</v>
       </c>
       <c r="F43" t="n">
-        <v>66.73</v>
+        <v>74.02</v>
       </c>
       <c r="G43" t="n">
-        <v>0.34</v>
+        <v>0.49</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>HINDCON</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hindcon Chemicals Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>35.05</v>
+        <v>389.15</v>
       </c>
       <c r="D44" t="n">
-        <v>23.55</v>
+        <v>338.1</v>
       </c>
       <c r="E44" t="n">
-        <v>48.8</v>
+        <v>15.1</v>
       </c>
       <c r="F44" t="n">
-        <v>68.34</v>
+        <v>66.73</v>
       </c>
       <c r="G44" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>23-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SGIL</t>
+          <t>HINDCON</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SYNERGY GREEN INDUSTRIES LIMITED</t>
+          <t>Hindcon Chemicals Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>666.2</v>
+        <v>35.05</v>
       </c>
       <c r="D45" t="n">
-        <v>593.62</v>
+        <v>23.55</v>
       </c>
       <c r="E45" t="n">
-        <v>12.2</v>
+        <v>48.8</v>
       </c>
       <c r="F45" t="n">
-        <v>74.02</v>
+        <v>68.34</v>
       </c>
       <c r="G45" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>23-09-2026</t>
         </is>
       </c>
     </row>
@@ -14265,7 +14265,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -14275,7 +14275,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -14315,7 +14315,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -14335,7 +14335,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">

--- a/output/2026-10-01/enriched_analysis.xlsx
+++ b/output/2026-10-01/enriched_analysis.xlsx
@@ -4649,7 +4649,7 @@
         <v>7.91</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
@@ -6041,7 +6041,7 @@
         <v>11.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE24" t="b">
         <v>1</v>
@@ -10659,7 +10659,7 @@
         <v>4.96</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE44" t="b">
         <v>1</v>
